--- a/data/processed_data/Video_prueba/contracciones_Video_prueba.xlsx
+++ b/data/processed_data/Video_prueba/contracciones_Video_prueba.xlsx
@@ -26,16 +26,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -46,7 +43,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -54,21 +51,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -438,22 +426,22 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>k</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>umbral_px</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>eventos</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>falsos_control</t>
         </is>
@@ -796,112 +784,112 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>grupo</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>cinetica_min_frames</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>n_eventos_cinetica</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>amplitud_relativa_pct</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>amplitud_relativa_iqr_pct</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>ttp_n_eventos</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>ttp_n_medibles</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>ttp_frames_mediana</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>ttp_reportable</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>ttp_s</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>ttp_iqr_s</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>ttp_cota_inf_s</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>ttp_cota_sup_s</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>rt50_n_eventos</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>rt50_n_medibles</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>rt50_frames_mediana</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>rt50_reportable</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>rt50_s</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>rt50_iqr_s</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>rt50_cota_inf_s</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>rt50_cota_sup_s</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>cinetica_motivo</t>
         </is>
@@ -1120,322 +1108,322 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>canal</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>fps</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>n_frames</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>duracion_s</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>signo</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>ruido_canal_px</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>ruido_grosor_px</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>n_eventos</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>k_usado</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>k_automatico</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>hay_meseta</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>meseta_motivo</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>meseta_k_rango</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>conteo_reportable</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>intervalo_mediano_s</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>amplitud_traslacion_px</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>ritmo</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>fps_medido</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>adelgazamiento_px</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>adelgazamiento_sigma</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>retardo_adelgazamiento_s</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>cociente_adelg_trasl_pct</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>adelgazamiento_robusto_px</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>adelgazamiento_robusto_sigma</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>cociente_robusto_pct</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>blur_px</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>blur_sigma</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>cinetica_grupo_principal</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>cinetica_min_frames</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>n_eventos_cinetica</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>amplitud_relativa_pct</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>amplitud_relativa_iqr_pct</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>ttp_n_eventos</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>ttp_n_medibles</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>ttp_frames_mediana</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>ttp_reportable</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="AK1" t="inlineStr">
         <is>
           <t>ttp_s</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AL1" t="inlineStr">
         <is>
           <t>ttp_iqr_s</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AM1" t="inlineStr">
         <is>
           <t>ttp_cota_inf_s</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="AN1" t="inlineStr">
         <is>
           <t>ttp_cota_sup_s</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="AO1" t="inlineStr">
         <is>
           <t>rt50_n_eventos</t>
         </is>
       </c>
-      <c r="AP1" s="1" t="inlineStr">
+      <c r="AP1" t="inlineStr">
         <is>
           <t>rt50_n_medibles</t>
         </is>
       </c>
-      <c r="AQ1" s="1" t="inlineStr">
+      <c r="AQ1" t="inlineStr">
         <is>
           <t>rt50_frames_mediana</t>
         </is>
       </c>
-      <c r="AR1" s="1" t="inlineStr">
+      <c r="AR1" t="inlineStr">
         <is>
           <t>rt50_reportable</t>
         </is>
       </c>
-      <c r="AS1" s="1" t="inlineStr">
+      <c r="AS1" t="inlineStr">
         <is>
           <t>rt50_s</t>
         </is>
       </c>
-      <c r="AT1" s="1" t="inlineStr">
+      <c r="AT1" t="inlineStr">
         <is>
           <t>rt50_iqr_s</t>
         </is>
       </c>
-      <c r="AU1" s="1" t="inlineStr">
+      <c r="AU1" t="inlineStr">
         <is>
           <t>rt50_cota_inf_s</t>
         </is>
       </c>
-      <c r="AV1" s="1" t="inlineStr">
+      <c r="AV1" t="inlineStr">
         <is>
           <t>rt50_cota_sup_s</t>
         </is>
       </c>
-      <c r="AW1" s="1" t="inlineStr">
+      <c r="AW1" t="inlineStr">
         <is>
           <t>cinetica_motivo</t>
         </is>
       </c>
-      <c r="AX1" s="1" t="inlineStr">
+      <c r="AX1" t="inlineStr">
         <is>
           <t>fotogramas_sin_medida</t>
         </is>
       </c>
-      <c r="AY1" s="1" t="inlineStr">
+      <c r="AY1" t="inlineStr">
         <is>
           <t>fotogramas_sin_medida_pct</t>
         </is>
       </c>
-      <c r="AZ1" s="1" t="inlineStr">
+      <c r="AZ1" t="inlineStr">
         <is>
           <t>fotogramas_low_quality</t>
         </is>
       </c>
-      <c r="BA1" s="1" t="inlineStr">
+      <c r="BA1" t="inlineStr">
         <is>
           <t>eventos_junto_a_hueco</t>
         </is>
       </c>
-      <c r="BB1" s="1" t="inlineStr">
+      <c r="BB1" t="inlineStr">
         <is>
           <t>eventos_junto_al_borde</t>
         </is>
       </c>
-      <c r="BC1" s="1" t="inlineStr">
+      <c r="BC1" t="inlineStr">
         <is>
           <t>win_s_usado</t>
         </is>
       </c>
-      <c r="BD1" s="1" t="inlineStr">
+      <c r="BD1" t="inlineStr">
         <is>
           <t>win_s_automatico</t>
         </is>
       </c>
-      <c r="BE1" s="1" t="inlineStr">
+      <c r="BE1" t="inlineStr">
         <is>
           <t>duracion_evento_max_s</t>
         </is>
       </c>
-      <c r="BF1" s="1" t="inlineStr">
+      <c r="BF1" t="inlineStr">
         <is>
           <t>ventana_corta</t>
         </is>
       </c>
-      <c r="BG1" s="1" t="inlineStr">
+      <c r="BG1" t="inlineStr">
         <is>
           <t>conteo_por_ventana</t>
         </is>
       </c>
-      <c r="BH1" s="1" t="inlineStr">
+      <c r="BH1" t="inlineStr">
         <is>
           <t>conteo_estable_ventana</t>
         </is>
       </c>
-      <c r="BI1" s="1" t="inlineStr">
+      <c r="BI1" t="inlineStr">
         <is>
           <t>mesetas</t>
         </is>
       </c>
-      <c r="BJ1" s="1" t="inlineStr">
+      <c r="BJ1" t="inlineStr">
         <is>
           <t>ruido_borde_sup_px</t>
         </is>
       </c>
-      <c r="BK1" s="1" t="inlineStr">
+      <c r="BK1" t="inlineStr">
         <is>
           <t>ruido_borde_inf_px</t>
         </is>
       </c>
-      <c r="BL1" s="1" t="inlineStr">
+      <c r="BL1" t="inlineStr">
         <is>
           <t>cociente_ruido_bordes</t>
         </is>
@@ -1705,52 +1693,52 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>grupo</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>n</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>t_inicio_s</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>t_fin_s</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>intervalo_mediano_s</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>intervalo_IQR_s</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>frecuencia_mediana_Hz</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>CV_intervalo_pct</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>amplitud_mediana_px</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>amplitud_IQR_px</t>
         </is>
@@ -1839,87 +1827,87 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>tren</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>busqueda</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>veredicto</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>clasificacion</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>periodo_s</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>periodo_err_s</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>frecuencia_Hz</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>jitter_ms</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>z</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>p_valor</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>n_eventos_tren</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>n_ranuras</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>captura_pct</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>n_dudosos</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>n_sacados_tiempo_amplitud</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>inicio_s</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>fin_s</t>
         </is>
@@ -1999,32 +1987,32 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>tren</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>indice_evento</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>tiempo_s</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>desvio_s</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>amplitud</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>amplitud_mediana_tren</t>
         </is>
@@ -2065,32 +2053,32 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>tren</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>ranura</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>t_esperado_s</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>t_medido_s</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>error_s</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>capturada</t>
         </is>
@@ -2231,17 +2219,17 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>tiempo_s</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>intervalo_s</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>frecuencia_Hz</t>
         </is>
@@ -2504,27 +2492,27 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>evento</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>tiempo_s</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>amplitud_px</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>junto_a_hueco</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>junto_al_borde</t>
         </is>
@@ -3038,117 +3026,117 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>evento</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>grupo</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>tren</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>frame_pico</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>tiempo_s</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>amplitud_px</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>grosor_reposo_px</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>amplitud_relativa_pct</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>meseta_pico_frames</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>onset_s</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>ttp_frames</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>ttp_s</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>ttp_min_s</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>ttp_max_s</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>ttp_medible</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>rt50_frames</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>rt50_s</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>rt50_min_s</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>rt50_max_s</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>rt50_medible</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>offset_s</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>duracion_frames</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>duracion_s</t>
         </is>

--- a/data/processed_data/Video_prueba/contracciones_Video_prueba.xlsx
+++ b/data/processed_data/Video_prueba/contracciones_Video_prueba.xlsx
@@ -780,7 +780,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V4"/>
+  <dimension ref="A1:W4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -811,85 +811,90 @@
       </c>
       <c r="F1" t="inlineStr">
         <is>
+          <t>amplitud_px</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
           <t>ttp_n_eventos</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>ttp_n_medibles</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>ttp_frames_mediana</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>ttp_reportable</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>ttp_s</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>ttp_iqr_s</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>ttp_cota_inf_s</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>ttp_cota_sup_s</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>rt50_n_eventos</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>rt50_n_medibles</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>rt50_frames_mediana</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>rt50_reportable</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>rt50_s</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>rt50_iqr_s</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>rt50_cota_inf_s</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>rt50_cota_sup_s</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>cinetica_motivo</t>
         </is>
@@ -916,46 +921,49 @@
         </is>
       </c>
       <c r="F2" t="n">
+        <v>2.093700000000013</v>
+      </c>
+      <c r="G2" t="n">
         <v>29</v>
       </c>
-      <c r="G2" t="n">
-        <v>0</v>
-      </c>
       <c r="H2" t="n">
-        <v>2</v>
-      </c>
-      <c r="I2" t="b">
-        <v>0</v>
-      </c>
-      <c r="J2" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="I2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J2" t="b">
+        <v>0</v>
+      </c>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="n">
-        <v>0</v>
-      </c>
+      <c r="L2" t="inlineStr"/>
       <c r="M2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" t="n">
         <v>0.1016666666666666</v>
       </c>
-      <c r="N2" t="n">
+      <c r="O2" t="n">
         <v>29</v>
       </c>
-      <c r="O2" t="n">
-        <v>0</v>
-      </c>
       <c r="P2" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q2" t="b">
-        <v>0</v>
-      </c>
-      <c r="R2" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>2</v>
+      </c>
+      <c r="R2" t="b">
+        <v>0</v>
+      </c>
       <c r="S2" t="inlineStr"/>
-      <c r="T2" t="n">
-        <v>0</v>
-      </c>
+      <c r="T2" t="inlineStr"/>
       <c r="U2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V2" t="n">
         <v>0.1016666666666683</v>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>TTP: medible en 0 de 29 eventos (&lt; la mitad con &gt;= 5 fotogramas); solo cota TTP &lt; 102 ms; RT50: medible en 0 de 29 eventos (&lt; la mitad con &gt;= 5 fotogramas); solo cota RT50 &lt; 102 ms</t>
         </is>
@@ -982,46 +990,49 @@
         </is>
       </c>
       <c r="F3" t="n">
+        <v>6.807450000000017</v>
+      </c>
+      <c r="G3" t="n">
         <v>6</v>
       </c>
-      <c r="G3" t="n">
-        <v>0</v>
-      </c>
       <c r="H3" t="n">
-        <v>2</v>
-      </c>
-      <c r="I3" t="b">
-        <v>0</v>
-      </c>
-      <c r="J3" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="I3" t="n">
+        <v>2</v>
+      </c>
+      <c r="J3" t="b">
+        <v>0</v>
+      </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="n">
-        <v>0</v>
-      </c>
+      <c r="L3" t="inlineStr"/>
       <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="n">
         <v>0.1008333333333331</v>
       </c>
-      <c r="N3" t="n">
+      <c r="O3" t="n">
         <v>6</v>
       </c>
-      <c r="O3" t="n">
-        <v>0</v>
-      </c>
       <c r="P3" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q3" t="b">
-        <v>0</v>
-      </c>
-      <c r="R3" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>2</v>
+      </c>
+      <c r="R3" t="b">
+        <v>0</v>
+      </c>
       <c r="S3" t="inlineStr"/>
-      <c r="T3" t="n">
-        <v>0</v>
-      </c>
+      <c r="T3" t="inlineStr"/>
       <c r="U3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V3" t="n">
         <v>0.1008333333333304</v>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>TTP: medible en 0 de 6 eventos (&lt; la mitad con &gt;= 5 fotogramas); solo cota TTP &lt; 101 ms; RT50: medible en 0 de 6 eventos (&lt; la mitad con &gt;= 5 fotogramas); solo cota RT50 &lt; 101 ms</t>
         </is>
@@ -1048,46 +1059,49 @@
         </is>
       </c>
       <c r="F4" t="n">
+        <v>2.07185000000004</v>
+      </c>
+      <c r="G4" t="n">
         <v>23</v>
       </c>
-      <c r="G4" t="n">
-        <v>0</v>
-      </c>
       <c r="H4" t="n">
-        <v>2</v>
-      </c>
-      <c r="I4" t="b">
-        <v>0</v>
-      </c>
-      <c r="J4" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="I4" t="n">
+        <v>2</v>
+      </c>
+      <c r="J4" t="b">
+        <v>0</v>
+      </c>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="n">
-        <v>0</v>
-      </c>
+      <c r="L4" t="inlineStr"/>
       <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="n">
         <v>0.1016666666666666</v>
       </c>
-      <c r="N4" t="n">
+      <c r="O4" t="n">
         <v>23</v>
       </c>
-      <c r="O4" t="n">
-        <v>0</v>
-      </c>
       <c r="P4" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q4" t="b">
-        <v>0</v>
-      </c>
-      <c r="R4" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>2</v>
+      </c>
+      <c r="R4" t="b">
+        <v>0</v>
+      </c>
       <c r="S4" t="inlineStr"/>
-      <c r="T4" t="n">
-        <v>0</v>
-      </c>
+      <c r="T4" t="inlineStr"/>
       <c r="U4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V4" t="n">
         <v>0.1033333333333335</v>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>TTP: medible en 0 de 23 eventos (&lt; la mitad con &gt;= 5 fotogramas); solo cota TTP &lt; 102 ms; RT50: medible en 0 de 23 eventos (&lt; la mitad con &gt;= 5 fotogramas); solo cota RT50 &lt; 103 ms</t>
         </is>
@@ -1104,7 +1118,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BL2"/>
+  <dimension ref="A1:BM2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1270,160 +1284,165 @@
       </c>
       <c r="AG1" t="inlineStr">
         <is>
+          <t>amplitud_px</t>
+        </is>
+      </c>
+      <c r="AH1" t="inlineStr">
+        <is>
           <t>ttp_n_eventos</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>ttp_n_medibles</t>
         </is>
       </c>
-      <c r="AI1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>ttp_frames_mediana</t>
         </is>
       </c>
-      <c r="AJ1" t="inlineStr">
+      <c r="AK1" t="inlineStr">
         <is>
           <t>ttp_reportable</t>
         </is>
       </c>
-      <c r="AK1" t="inlineStr">
+      <c r="AL1" t="inlineStr">
         <is>
           <t>ttp_s</t>
         </is>
       </c>
-      <c r="AL1" t="inlineStr">
+      <c r="AM1" t="inlineStr">
         <is>
           <t>ttp_iqr_s</t>
         </is>
       </c>
-      <c r="AM1" t="inlineStr">
+      <c r="AN1" t="inlineStr">
         <is>
           <t>ttp_cota_inf_s</t>
         </is>
       </c>
-      <c r="AN1" t="inlineStr">
+      <c r="AO1" t="inlineStr">
         <is>
           <t>ttp_cota_sup_s</t>
         </is>
       </c>
-      <c r="AO1" t="inlineStr">
+      <c r="AP1" t="inlineStr">
         <is>
           <t>rt50_n_eventos</t>
         </is>
       </c>
-      <c r="AP1" t="inlineStr">
+      <c r="AQ1" t="inlineStr">
         <is>
           <t>rt50_n_medibles</t>
         </is>
       </c>
-      <c r="AQ1" t="inlineStr">
+      <c r="AR1" t="inlineStr">
         <is>
           <t>rt50_frames_mediana</t>
         </is>
       </c>
-      <c r="AR1" t="inlineStr">
+      <c r="AS1" t="inlineStr">
         <is>
           <t>rt50_reportable</t>
         </is>
       </c>
-      <c r="AS1" t="inlineStr">
+      <c r="AT1" t="inlineStr">
         <is>
           <t>rt50_s</t>
         </is>
       </c>
-      <c r="AT1" t="inlineStr">
+      <c r="AU1" t="inlineStr">
         <is>
           <t>rt50_iqr_s</t>
         </is>
       </c>
-      <c r="AU1" t="inlineStr">
+      <c r="AV1" t="inlineStr">
         <is>
           <t>rt50_cota_inf_s</t>
         </is>
       </c>
-      <c r="AV1" t="inlineStr">
+      <c r="AW1" t="inlineStr">
         <is>
           <t>rt50_cota_sup_s</t>
         </is>
       </c>
-      <c r="AW1" t="inlineStr">
+      <c r="AX1" t="inlineStr">
         <is>
           <t>cinetica_motivo</t>
         </is>
       </c>
-      <c r="AX1" t="inlineStr">
+      <c r="AY1" t="inlineStr">
         <is>
           <t>fotogramas_sin_medida</t>
         </is>
       </c>
-      <c r="AY1" t="inlineStr">
+      <c r="AZ1" t="inlineStr">
         <is>
           <t>fotogramas_sin_medida_pct</t>
         </is>
       </c>
-      <c r="AZ1" t="inlineStr">
+      <c r="BA1" t="inlineStr">
         <is>
           <t>fotogramas_low_quality</t>
         </is>
       </c>
-      <c r="BA1" t="inlineStr">
+      <c r="BB1" t="inlineStr">
         <is>
           <t>eventos_junto_a_hueco</t>
         </is>
       </c>
-      <c r="BB1" t="inlineStr">
+      <c r="BC1" t="inlineStr">
         <is>
           <t>eventos_junto_al_borde</t>
         </is>
       </c>
-      <c r="BC1" t="inlineStr">
+      <c r="BD1" t="inlineStr">
         <is>
           <t>win_s_usado</t>
         </is>
       </c>
-      <c r="BD1" t="inlineStr">
+      <c r="BE1" t="inlineStr">
         <is>
           <t>win_s_automatico</t>
         </is>
       </c>
-      <c r="BE1" t="inlineStr">
+      <c r="BF1" t="inlineStr">
         <is>
           <t>duracion_evento_max_s</t>
         </is>
       </c>
-      <c r="BF1" t="inlineStr">
+      <c r="BG1" t="inlineStr">
         <is>
           <t>ventana_corta</t>
         </is>
       </c>
-      <c r="BG1" t="inlineStr">
+      <c r="BH1" t="inlineStr">
         <is>
           <t>conteo_por_ventana</t>
         </is>
       </c>
-      <c r="BH1" t="inlineStr">
+      <c r="BI1" t="inlineStr">
         <is>
           <t>conteo_estable_ventana</t>
         </is>
       </c>
-      <c r="BI1" t="inlineStr">
+      <c r="BJ1" t="inlineStr">
         <is>
           <t>mesetas</t>
         </is>
       </c>
-      <c r="BJ1" t="inlineStr">
+      <c r="BK1" t="inlineStr">
         <is>
           <t>ruido_borde_sup_px</t>
         </is>
       </c>
-      <c r="BK1" t="inlineStr">
+      <c r="BL1" t="inlineStr">
         <is>
           <t>ruido_borde_inf_px</t>
         </is>
       </c>
-      <c r="BL1" t="inlineStr">
+      <c r="BM1" t="inlineStr">
         <is>
           <t>cociente_ruido_bordes</t>
         </is>
@@ -1500,9 +1519,9 @@
        'estimulados', 'estimulados', 'estimulados', 'estimulados',
        'estimulados'], dtype=object), 'tren_por_evento': array([0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 1, 0, 0,
        0, 0, 1, 1, 1, 1, 1]), 'estimulados': array([19, 24, 25, 26, 27, 28]), 'estimulados_dudosos': array([], dtype=int64), 'espontaneos': array([ 0,  1,  2,  3,  4,  5,  6,  7,  8,  9, 10, 11, 12, 13, 14, 15, 16,
-       17, 18, 20, 21, 22, 23]), 'hay_estimulacion': True, 'n_trenes_estimulados': 1, 'tren_principal': 1, 'veredicto': 'enganchado a la frecuencia configurada (0.1 Hz)', 'z': 17.248, 'p_valor': 0.000999000999000999, 'periodo_grilla_s': 9.9682, 'periodo_s': 10.00043, 'periodo_err_s': 0.0023, 'frecuencia_Hz': 0.1, 'frecuencia_err_Hz': 2.3e-05, 'jitter_s': np.float64(0.00962), 'tolerancia_s': 0.0667, 'n_estimulados': 6, 'n_ranuras': 6, 'tasa_captura_pct': 100.0, 'tren_inicio_s': 14.875, 'tren_fin_s': 64.875, 'jitter_limitado_por_resolucion': True, 'resumen_grupos':          grupo   n  ...  amplitud_mediana_px  amplitud_IQR_px
-0  estimulados   6  ...               6.8075           0.2705
-1  espontaneos  23  ...               2.0719           0.1889
+       17, 18, 20, 21, 22, 23]), 'hay_estimulacion': True, 'n_trenes_estimulados': 1, 'tren_principal': 1, 'veredicto': 'enganchado a la frecuencia configurada (0.1 Hz)', 'z': 17.248, 'p_valor': 0.000999000999000999, 'periodo_grilla_s': 9.9682, 'periodo_s': 10.00043, 'periodo_err_s': 0.0023, 'frecuencia_Hz': 0.1, 'frecuencia_err_Hz': 2.3e-05, 'jitter_s': np.float64(0.00962), 'tolerancia_s': 0.0667, 'n_estimulados': 6, 'n_ranuras': 6, 'tasa_captura_pct': 100.0, 'tren_inicio_s': 14.875, 'tren_fin_s': 64.875, 'jitter_limitado_por_resolucion': True, 'resumen_grupos':          grupo   n  t_inicio_s  ...  CV_intervalo_pct  amplitud_mediana_px  amplitud_IQR_px
+0  estimulados   6       14.87  ...               0.0               6.8075           0.2705
+1  espontaneos  23        0.28  ...              90.6               2.0719           0.1889
 [2 rows x 10 columns], 'espontaneas_instantanea':     tiempo_s  intervalo_s  frecuencia_Hz
 0      0.569       0.5813         1.7204
 1      1.139       0.5593         1.7880
@@ -1584,53 +1603,53 @@
         </is>
       </c>
       <c r="AG2" t="n">
+        <v>6.807450000000017</v>
+      </c>
+      <c r="AH2" t="n">
         <v>6</v>
       </c>
-      <c r="AH2" t="n">
-        <v>0</v>
-      </c>
       <c r="AI2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AJ2" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK2" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK2" t="b">
+        <v>0</v>
+      </c>
       <c r="AL2" t="inlineStr"/>
-      <c r="AM2" t="n">
-        <v>0</v>
-      </c>
+      <c r="AM2" t="inlineStr"/>
       <c r="AN2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO2" t="n">
         <v>0.1008333333333331</v>
       </c>
-      <c r="AO2" t="n">
+      <c r="AP2" t="n">
         <v>6</v>
       </c>
-      <c r="AP2" t="n">
-        <v>0</v>
-      </c>
       <c r="AQ2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AR2" t="b">
-        <v>0</v>
-      </c>
-      <c r="AS2" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AS2" t="b">
+        <v>0</v>
+      </c>
       <c r="AT2" t="inlineStr"/>
-      <c r="AU2" t="n">
-        <v>0</v>
-      </c>
+      <c r="AU2" t="inlineStr"/>
       <c r="AV2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW2" t="n">
         <v>0.1008333333333304</v>
       </c>
-      <c r="AW2" t="inlineStr">
+      <c r="AX2" t="inlineStr">
         <is>
           <t>TTP: medible en 0 de 6 eventos (&lt; la mitad con &gt;= 5 fotogramas); solo cota TTP &lt; 101 ms; RT50: medible en 0 de 6 eventos (&lt; la mitad con &gt;= 5 fotogramas); solo cota RT50 &lt; 101 ms</t>
         </is>
       </c>
-      <c r="AX2" t="n">
-        <v>0</v>
-      </c>
       <c r="AY2" t="n">
         <v>0</v>
       </c>
@@ -1641,40 +1660,43 @@
         <v>0</v>
       </c>
       <c r="BB2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BC2" t="n">
         <v>2</v>
       </c>
-      <c r="BD2" t="b">
-        <v>1</v>
-      </c>
-      <c r="BE2" t="n">
+      <c r="BD2" t="n">
+        <v>2</v>
+      </c>
+      <c r="BE2" t="b">
+        <v>1</v>
+      </c>
+      <c r="BF2" t="n">
         <v>0.2333333333333201</v>
       </c>
-      <c r="BF2" t="b">
-        <v>0</v>
-      </c>
-      <c r="BG2" t="inlineStr">
+      <c r="BG2" t="b">
+        <v>0</v>
+      </c>
+      <c r="BH2" t="inlineStr">
         <is>
           <t>1.5 s: 29 | 2 s: 29 | 3 s: 29</t>
         </is>
       </c>
-      <c r="BH2" t="b">
-        <v>1</v>
-      </c>
-      <c r="BI2" t="inlineStr">
+      <c r="BI2" t="b">
+        <v>1</v>
+      </c>
+      <c r="BJ2" t="inlineStr">
         <is>
           <t>29 ev en k=5.315-15.163</t>
         </is>
       </c>
-      <c r="BJ2" t="n">
+      <c r="BK2" t="n">
         <v>0.1095641400000554</v>
       </c>
-      <c r="BK2" t="n">
+      <c r="BL2" t="n">
         <v>0.08569428000006364</v>
       </c>
-      <c r="BL2" t="n">
+      <c r="BM2" t="n">
         <v>1.278546712802465</v>
       </c>
     </row>

--- a/data/processed_data/Video_prueba/contracciones_Video_prueba.xlsx
+++ b/data/processed_data/Video_prueba/contracciones_Video_prueba.xlsx
@@ -1,22 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="estab_Video_prueba" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="resumen_Video_prueba" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="ritmo_Video_prueba" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="trenes_Video_prueba" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="sacados_Video_prueba" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="grilla_Video_prueba" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="espont_Video_prueba" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="eventos_Video_prueba" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="cinetica_Video_prueba" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="cin_grupos_Video_prueba" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="estab_Video_prueba" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="resumen_Video_prueba" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ritmo_Video_prueba" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="trenes_Video_prueba" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="sacados_Video_prueba" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="grilla_Video_prueba" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="espont_Video_prueba" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="eventos_Video_prueba" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="basal_Video_prueba" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="cinetica_Video_prueba" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="cin_grupos_Video_prueba" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -780,15 +781,2539 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W4"/>
+  <dimension ref="A1:Z30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
+          <t>evento</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
           <t>grupo</t>
         </is>
       </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>tren</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>frame_pico</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>tiempo_s</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>amplitud_px</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>grosor_reposo_px</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>amplitud_relativa_pct</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>meseta_pico_frames</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>frame_llega_max</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>tiempo_llega_max_s</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>pico_dudoso_por_ruido</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>onset_s</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>ttp_frames</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>ttp_s</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>ttp_min_s</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>ttp_max_s</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>ttp_medible</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>rt50_frames</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rt50_s</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rt50_min_s</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>rt50_max_s</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>rt50_medible</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>offset_s</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>duracion_frames</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>duracion_s</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>espontaneos</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2" t="n">
+        <v>11</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.3383333333333334</v>
+      </c>
+      <c r="F2" t="n">
+        <v>2.07185000000004</v>
+      </c>
+      <c r="G2" t="n">
+        <v>294.186442631115</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.7042642691043263</v>
+      </c>
+      <c r="I2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J2" t="n">
+        <v>11</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0.3383333333333334</v>
+      </c>
+      <c r="L2" t="b">
+        <v>1</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0.277989655707567</v>
+      </c>
+      <c r="N2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0.06034367762576642</v>
+      </c>
+      <c r="P2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>0.09833333333333333</v>
+      </c>
+      <c r="R2" t="b">
+        <v>0</v>
+      </c>
+      <c r="S2" t="n">
+        <v>2</v>
+      </c>
+      <c r="T2" t="n">
+        <v>0.04847599810750691</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V2" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="W2" t="b">
+        <v>0</v>
+      </c>
+      <c r="X2" t="n">
+        <v>0.4330979839398581</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>0.1551083282322911</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>espontaneos</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3" t="n">
+        <v>28</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="F3" t="n">
+        <v>1.911099999999976</v>
+      </c>
+      <c r="G3" t="n">
+        <v>294.1858218643114</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.6496234209687513</v>
+      </c>
+      <c r="I3" t="n">
+        <v>2</v>
+      </c>
+      <c r="J3" t="n">
+        <v>28</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="L3" t="b">
+        <v>1</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.8592479658844149</v>
+      </c>
+      <c r="N3" t="n">
+        <v>2</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0.05075203411558515</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0.1333333333333333</v>
+      </c>
+      <c r="R3" t="b">
+        <v>0</v>
+      </c>
+      <c r="S3" t="n">
+        <v>3</v>
+      </c>
+      <c r="T3" t="n">
+        <v>0.06212855624788582</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V3" t="n">
+        <v>0.1416666666666663</v>
+      </c>
+      <c r="W3" t="b">
+        <v>0</v>
+      </c>
+      <c r="X3" t="n">
+        <v>1.032840827980012</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>0.1735928620955974</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>espontaneos</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" t="n">
+        <v>45</v>
+      </c>
+      <c r="E4" t="n">
+        <v>1.471666666666667</v>
+      </c>
+      <c r="F4" t="n">
+        <v>2.083199999999977</v>
+      </c>
+      <c r="G4" t="n">
+        <v>294.2004470505329</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.7080886589006981</v>
+      </c>
+      <c r="I4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J4" t="n">
+        <v>45</v>
+      </c>
+      <c r="K4" t="n">
+        <v>1.471666666666667</v>
+      </c>
+      <c r="L4" t="b">
+        <v>1</v>
+      </c>
+      <c r="M4" t="n">
+        <v>1.41853570329332</v>
+      </c>
+      <c r="N4" t="n">
+        <v>2</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.05313096337334677</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0.1083333333333329</v>
+      </c>
+      <c r="R4" t="b">
+        <v>0</v>
+      </c>
+      <c r="S4" t="n">
+        <v>3</v>
+      </c>
+      <c r="T4" t="n">
+        <v>0.07726777939042195</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0.02500000000000013</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0.133333333333334</v>
+      </c>
+      <c r="W4" t="b">
+        <v>0</v>
+      </c>
+      <c r="X4" t="n">
+        <v>1.598569790012352</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>0.180034086719032</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>espontaneos</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" t="n">
+        <v>62</v>
+      </c>
+      <c r="E5" t="n">
+        <v>2.038333333333334</v>
+      </c>
+      <c r="F5" t="n">
+        <v>2.518399999999986</v>
+      </c>
+      <c r="G5" t="n">
+        <v>294.2096897179215</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.8559881227618792</v>
+      </c>
+      <c r="I5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J5" t="n">
+        <v>62</v>
+      </c>
+      <c r="K5" t="n">
+        <v>2.038333333333334</v>
+      </c>
+      <c r="L5" t="b">
+        <v>1</v>
+      </c>
+      <c r="M5" t="n">
+        <v>1.982052650145516</v>
+      </c>
+      <c r="N5" t="n">
+        <v>2</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.05628068318781798</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0.1000000000000003</v>
+      </c>
+      <c r="R5" t="b">
+        <v>0</v>
+      </c>
+      <c r="S5" t="n">
+        <v>2</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0.05580770747092556</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0.09333333333333282</v>
+      </c>
+      <c r="W5" t="b">
+        <v>0</v>
+      </c>
+      <c r="X5" t="n">
+        <v>2.14553618388036</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>0.1634835337348437</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>espontaneos</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" t="n">
+        <v>79</v>
+      </c>
+      <c r="E6" t="n">
+        <v>2.605</v>
+      </c>
+      <c r="F6" t="n">
+        <v>2.356300000000033</v>
+      </c>
+      <c r="G6" t="n">
+        <v>294.2180072554886</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.8008687238350795</v>
+      </c>
+      <c r="I6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J6" t="n">
+        <v>79</v>
+      </c>
+      <c r="K6" t="n">
+        <v>2.605</v>
+      </c>
+      <c r="L6" t="b">
+        <v>1</v>
+      </c>
+      <c r="M6" t="n">
+        <v>2.553522137404581</v>
+      </c>
+      <c r="N6" t="n">
+        <v>2</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.05147786259541931</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0.09833333333333316</v>
+      </c>
+      <c r="R6" t="b">
+        <v>0</v>
+      </c>
+      <c r="S6" t="n">
+        <v>2</v>
+      </c>
+      <c r="T6" t="n">
+        <v>0.06237304750793804</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0.1000000000000001</v>
+      </c>
+      <c r="W6" t="b">
+        <v>0</v>
+      </c>
+      <c r="X6" t="n">
+        <v>2.708330000000001</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>0.1548078625954203</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>espontaneos</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" t="n">
+        <v>96</v>
+      </c>
+      <c r="E7" t="n">
+        <v>3.171666666666667</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1.922900000000027</v>
+      </c>
+      <c r="G7" t="n">
+        <v>294.2257620822636</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.6535457624075749</v>
+      </c>
+      <c r="I7" t="n">
+        <v>2</v>
+      </c>
+      <c r="J7" t="n">
+        <v>96</v>
+      </c>
+      <c r="K7" t="n">
+        <v>3.171666666666667</v>
+      </c>
+      <c r="L7" t="b">
+        <v>1</v>
+      </c>
+      <c r="M7" t="n">
+        <v>3.127293428757324</v>
+      </c>
+      <c r="N7" t="n">
+        <v>2</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0.04437323790934311</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0.1333333333333342</v>
+      </c>
+      <c r="R7" t="b">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
+        <v>3</v>
+      </c>
+      <c r="T7" t="n">
+        <v>0.0682990182060812</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" t="n">
+        <v>0.1333333333333329</v>
+      </c>
+      <c r="W7" t="b">
+        <v>0</v>
+      </c>
+      <c r="X7" t="n">
+        <v>3.281085168239442</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>0.1537917394821178</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>espontaneos</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" t="n">
+        <v>113</v>
+      </c>
+      <c r="E8" t="n">
+        <v>3.736666666666667</v>
+      </c>
+      <c r="F8" t="n">
+        <v>2.043000000000006</v>
+      </c>
+      <c r="G8" t="n">
+        <v>294.1927371840957</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.6944427043151535</v>
+      </c>
+      <c r="I8" t="n">
+        <v>1</v>
+      </c>
+      <c r="J8" t="n">
+        <v>113</v>
+      </c>
+      <c r="K8" t="n">
+        <v>3.736666666666667</v>
+      </c>
+      <c r="L8" t="b">
+        <v>1</v>
+      </c>
+      <c r="M8" t="n">
+        <v>3.688532583577262</v>
+      </c>
+      <c r="N8" t="n">
+        <v>2</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.04813408308940481</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0.105</v>
+      </c>
+      <c r="R8" t="b">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>2</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0.07283428968874883</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" t="n">
+        <v>0.1083333333333329</v>
+      </c>
+      <c r="W8" t="b">
+        <v>0</v>
+      </c>
+      <c r="X8" t="n">
+        <v>3.845477477477479</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>0.1569448939002172</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>espontaneos</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" t="n">
+        <v>130</v>
+      </c>
+      <c r="E9" t="n">
+        <v>4.305000000000001</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1.953499999999963</v>
+      </c>
+      <c r="G9" t="n">
+        <v>294.1927371840957</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.6640204713067168</v>
+      </c>
+      <c r="I9" t="n">
+        <v>2</v>
+      </c>
+      <c r="J9" t="n">
+        <v>130</v>
+      </c>
+      <c r="K9" t="n">
+        <v>4.305000000000001</v>
+      </c>
+      <c r="L9" t="b">
+        <v>1</v>
+      </c>
+      <c r="M9" t="n">
+        <v>4.253494974191794</v>
+      </c>
+      <c r="N9" t="n">
+        <v>2</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.05150502580820682</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0.1333333333333337</v>
+      </c>
+      <c r="R9" t="b">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
+        <v>3</v>
+      </c>
+      <c r="T9" t="n">
+        <v>0.07340231680333265</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" t="n">
+        <v>0.1333333333333329</v>
+      </c>
+      <c r="W9" t="b">
+        <v>0</v>
+      </c>
+      <c r="X9" t="n">
+        <v>4.418203921568629</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>0.1647089473768348</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>espontaneos</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" t="n">
+        <v>147</v>
+      </c>
+      <c r="E10" t="n">
+        <v>4.871666666666667</v>
+      </c>
+      <c r="F10" t="n">
+        <v>2.0976</v>
+      </c>
+      <c r="G10" t="n">
+        <v>294.1914281912709</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.7130051384897008</v>
+      </c>
+      <c r="I10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J10" t="n">
+        <v>147</v>
+      </c>
+      <c r="K10" t="n">
+        <v>4.871666666666667</v>
+      </c>
+      <c r="L10" t="b">
+        <v>1</v>
+      </c>
+      <c r="M10" t="n">
+        <v>4.817098754578756</v>
+      </c>
+      <c r="N10" t="n">
+        <v>2</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0.05456791208791145</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0.09833333333333272</v>
+      </c>
+      <c r="R10" t="b">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
+        <v>2</v>
+      </c>
+      <c r="T10" t="n">
+        <v>0.06285318951238228</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" t="n">
+        <v>0.1016666666666657</v>
+      </c>
+      <c r="W10" t="b">
+        <v>0</v>
+      </c>
+      <c r="X10" t="n">
+        <v>4.980667027221918</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>0.163568272643162</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>espontaneos</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" t="n">
+        <v>164</v>
+      </c>
+      <c r="E11" t="n">
+        <v>5.446666666666667</v>
+      </c>
+      <c r="F11" t="n">
+        <v>2.093700000000013</v>
+      </c>
+      <c r="G11" t="n">
+        <v>294.1920858240017</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.7116778801631508</v>
+      </c>
+      <c r="I11" t="n">
+        <v>1</v>
+      </c>
+      <c r="J11" t="n">
+        <v>164</v>
+      </c>
+      <c r="K11" t="n">
+        <v>5.446666666666667</v>
+      </c>
+      <c r="L11" t="b">
+        <v>1</v>
+      </c>
+      <c r="M11" t="n">
+        <v>5.378556092306326</v>
+      </c>
+      <c r="N11" t="n">
+        <v>2</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0.0681105743603414</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0.1016666666666666</v>
+      </c>
+      <c r="R11" t="b">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
+        <v>2</v>
+      </c>
+      <c r="T11" t="n">
+        <v>0.05135885071328072</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" t="n">
+        <v>0.1133333333333333</v>
+      </c>
+      <c r="W11" t="b">
+        <v>0</v>
+      </c>
+      <c r="X11" t="n">
+        <v>5.586102227298683</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>0.2075461349923575</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>espontaneos</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" t="n">
+        <v>180</v>
+      </c>
+      <c r="E12" t="n">
+        <v>5.971666666666667</v>
+      </c>
+      <c r="F12" t="n">
+        <v>2.081199999999967</v>
+      </c>
+      <c r="G12" t="n">
+        <v>294.1757204680613</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.7074683106711124</v>
+      </c>
+      <c r="I12" t="n">
+        <v>1</v>
+      </c>
+      <c r="J12" t="n">
+        <v>180</v>
+      </c>
+      <c r="K12" t="n">
+        <v>5.971666666666667</v>
+      </c>
+      <c r="L12" t="b">
+        <v>1</v>
+      </c>
+      <c r="M12" t="n">
+        <v>5.91788425690561</v>
+      </c>
+      <c r="N12" t="n">
+        <v>2</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0.05378240976105708</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0.1083333333333334</v>
+      </c>
+      <c r="R12" t="b">
+        <v>0</v>
+      </c>
+      <c r="S12" t="n">
+        <v>3</v>
+      </c>
+      <c r="T12" t="n">
+        <v>0.07456235663406829</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0.02500000000000036</v>
+      </c>
+      <c r="V12" t="n">
+        <v>0.1333333333333346</v>
+      </c>
+      <c r="W12" t="b">
+        <v>0</v>
+      </c>
+      <c r="X12" t="n">
+        <v>6.099438589379813</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>0.1815543324742031</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>espontaneos</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" t="n">
+        <v>198</v>
+      </c>
+      <c r="E13" t="n">
+        <v>6.571666666666667</v>
+      </c>
+      <c r="F13" t="n">
+        <v>2.378100000000018</v>
+      </c>
+      <c r="G13" t="n">
+        <v>294.2090886717925</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.8083026974917583</v>
+      </c>
+      <c r="I13" t="n">
+        <v>1</v>
+      </c>
+      <c r="J13" t="n">
+        <v>198</v>
+      </c>
+      <c r="K13" t="n">
+        <v>6.571666666666667</v>
+      </c>
+      <c r="L13" t="b">
+        <v>1</v>
+      </c>
+      <c r="M13" t="n">
+        <v>6.508522902232486</v>
+      </c>
+      <c r="N13" t="n">
+        <v>3</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0.06314376443418102</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0.03000000000000025</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0.1333333333333337</v>
+      </c>
+      <c r="R13" t="b">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
+        <v>2</v>
+      </c>
+      <c r="T13" t="n">
+        <v>0.04022487482117132</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" t="n">
+        <v>0.1033333333333335</v>
+      </c>
+      <c r="W13" t="b">
+        <v>0</v>
+      </c>
+      <c r="X13" t="n">
+        <v>6.664180808080808</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>0.1556579058483214</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>espontaneos</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" t="n">
+        <v>209</v>
+      </c>
+      <c r="E14" t="n">
+        <v>7.28</v>
+      </c>
+      <c r="F14" t="n">
+        <v>2.12360000000001</v>
+      </c>
+      <c r="G14" t="n">
+        <v>294.1229333192731</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.7220110230897308</v>
+      </c>
+      <c r="I14" t="n">
+        <v>1</v>
+      </c>
+      <c r="J14" t="n">
+        <v>209</v>
+      </c>
+      <c r="K14" t="n">
+        <v>7.28</v>
+      </c>
+      <c r="L14" t="b">
+        <v>1</v>
+      </c>
+      <c r="M14" t="n">
+        <v>7.265851470196322</v>
+      </c>
+      <c r="N14" t="n">
+        <v>1</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0.01414852980367787</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0.03333333333333321</v>
+      </c>
+      <c r="R14" t="b">
+        <v>0</v>
+      </c>
+      <c r="S14" t="n">
+        <v>1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>0.008140141061024231</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" t="n">
+        <v>0.03333333333333321</v>
+      </c>
+      <c r="W14" t="b">
+        <v>0</v>
+      </c>
+      <c r="X14" t="n">
+        <v>7.294652253909844</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>0.02880078371352202</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>espontaneos</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" t="n">
+        <v>222</v>
+      </c>
+      <c r="E15" t="n">
+        <v>7.671666666666667</v>
+      </c>
+      <c r="F15" t="n">
+        <v>2.038999999999987</v>
+      </c>
+      <c r="G15" t="n">
+        <v>294.1707185111845</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.6931349286970123</v>
+      </c>
+      <c r="I15" t="n">
+        <v>1</v>
+      </c>
+      <c r="J15" t="n">
+        <v>222</v>
+      </c>
+      <c r="K15" t="n">
+        <v>7.671666666666667</v>
+      </c>
+      <c r="L15" t="b">
+        <v>1</v>
+      </c>
+      <c r="M15" t="n">
+        <v>7.610206812652068</v>
+      </c>
+      <c r="N15" t="n">
+        <v>2</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0.06145985401459875</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0.09999999999999964</v>
+      </c>
+      <c r="R15" t="b">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
+        <v>2</v>
+      </c>
+      <c r="T15" t="n">
+        <v>0.06134544667964548</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" t="n">
+        <v>0.1000000000000005</v>
+      </c>
+      <c r="W15" t="b">
+        <v>0</v>
+      </c>
+      <c r="X15" t="n">
+        <v>7.780480532638585</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>0.1702737199865165</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>espontaneos</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>0</v>
+      </c>
+      <c r="D16" t="n">
+        <v>240</v>
+      </c>
+      <c r="E16" t="n">
+        <v>8.283333333333333</v>
+      </c>
+      <c r="F16" t="n">
+        <v>2.130499999999984</v>
+      </c>
+      <c r="G16" t="n">
+        <v>294.2228176658223</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.7241110723165602</v>
+      </c>
+      <c r="I16" t="n">
+        <v>1</v>
+      </c>
+      <c r="J16" t="n">
+        <v>240</v>
+      </c>
+      <c r="K16" t="n">
+        <v>8.283333333333333</v>
+      </c>
+      <c r="L16" t="b">
+        <v>1</v>
+      </c>
+      <c r="M16" t="n">
+        <v>8.206060895395717</v>
+      </c>
+      <c r="N16" t="n">
+        <v>3</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0.07727243793761573</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0.02333333333333165</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0.1316666666666677</v>
+      </c>
+      <c r="R16" t="b">
+        <v>0</v>
+      </c>
+      <c r="S16" t="n">
+        <v>2</v>
+      </c>
+      <c r="T16" t="n">
+        <v>0.03071177337325892</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" t="n">
+        <v>0.1016666666666683</v>
+      </c>
+      <c r="W16" t="b">
+        <v>0</v>
+      </c>
+      <c r="X16" t="n">
+        <v>8.359612132624427</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>0.1535512372287098</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>espontaneos</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" t="n">
+        <v>272</v>
+      </c>
+      <c r="E17" t="n">
+        <v>9.338333333333335</v>
+      </c>
+      <c r="F17" t="n">
+        <v>2.008200000000045</v>
+      </c>
+      <c r="G17" t="n">
+        <v>294.1947370693252</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.6826090840390611</v>
+      </c>
+      <c r="I17" t="n">
+        <v>1</v>
+      </c>
+      <c r="J17" t="n">
+        <v>272</v>
+      </c>
+      <c r="K17" t="n">
+        <v>9.338333333333335</v>
+      </c>
+      <c r="L17" t="b">
+        <v>1</v>
+      </c>
+      <c r="M17" t="n">
+        <v>9.283307124765994</v>
+      </c>
+      <c r="N17" t="n">
+        <v>2</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0.05502620856734097</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0.1000000000000014</v>
+      </c>
+      <c r="R17" t="b">
+        <v>0</v>
+      </c>
+      <c r="S17" t="n">
+        <v>2</v>
+      </c>
+      <c r="T17" t="n">
+        <v>0.06638977509945043</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0</v>
+      </c>
+      <c r="V17" t="n">
+        <v>0.1033333333333335</v>
+      </c>
+      <c r="W17" t="b">
+        <v>0</v>
+      </c>
+      <c r="X17" t="n">
+        <v>9.454144519370622</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>0.1708373946046287</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>espontaneos</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D18" t="n">
+        <v>290</v>
+      </c>
+      <c r="E18" t="n">
+        <v>9.938333333333334</v>
+      </c>
+      <c r="F18" t="n">
+        <v>2.204099999999983</v>
+      </c>
+      <c r="G18" t="n">
+        <v>294.2034913291759</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.7491753378051785</v>
+      </c>
+      <c r="I18" t="n">
+        <v>1</v>
+      </c>
+      <c r="J18" t="n">
+        <v>290</v>
+      </c>
+      <c r="K18" t="n">
+        <v>9.938333333333334</v>
+      </c>
+      <c r="L18" t="b">
+        <v>1</v>
+      </c>
+      <c r="M18" t="n">
+        <v>9.884551580034749</v>
+      </c>
+      <c r="N18" t="n">
+        <v>2</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0.05378175329858514</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0.09999999999999964</v>
+      </c>
+      <c r="R18" t="b">
+        <v>0</v>
+      </c>
+      <c r="S18" t="n">
+        <v>3</v>
+      </c>
+      <c r="T18" t="n">
+        <v>0.0773669686169729</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0.0400000000000027</v>
+      </c>
+      <c r="V18" t="n">
+        <v>0.1316666666666695</v>
+      </c>
+      <c r="W18" t="b">
+        <v>0</v>
+      </c>
+      <c r="X18" t="n">
+        <v>10.07473637722517</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>0.1901847971904207</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>espontaneos</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>0</v>
+      </c>
+      <c r="D19" t="n">
+        <v>308</v>
+      </c>
+      <c r="E19" t="n">
+        <v>10.53833333333333</v>
+      </c>
+      <c r="F19" t="n">
+        <v>2.337699999999984</v>
+      </c>
+      <c r="G19" t="n">
+        <v>294.214226572169</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.7945570910135985</v>
+      </c>
+      <c r="I19" t="n">
+        <v>1</v>
+      </c>
+      <c r="J19" t="n">
+        <v>308</v>
+      </c>
+      <c r="K19" t="n">
+        <v>10.53833333333333</v>
+      </c>
+      <c r="L19" t="b">
+        <v>1</v>
+      </c>
+      <c r="M19" t="n">
+        <v>10.46726430976431</v>
+      </c>
+      <c r="N19" t="n">
+        <v>3</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0.07106902356901834</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0.04000000000000092</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0.13333333333334</v>
+      </c>
+      <c r="R19" t="b">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
+        <v>2</v>
+      </c>
+      <c r="T19" t="n">
+        <v>0.04524162297698275</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0</v>
+      </c>
+      <c r="V19" t="n">
+        <v>0.09333333333333016</v>
+      </c>
+      <c r="W19" t="b">
+        <v>0</v>
+      </c>
+      <c r="X19" t="n">
+        <v>10.63149036402569</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>0.1642260542613805</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>espontaneos</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>0</v>
+      </c>
+      <c r="D20" t="n">
+        <v>342</v>
+      </c>
+      <c r="E20" t="n">
+        <v>11.67166666666667</v>
+      </c>
+      <c r="F20" t="n">
+        <v>2.003600000000006</v>
+      </c>
+      <c r="G20" t="n">
+        <v>294.2496961314322</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.6809182902622473</v>
+      </c>
+      <c r="I20" t="n">
+        <v>1</v>
+      </c>
+      <c r="J20" t="n">
+        <v>342</v>
+      </c>
+      <c r="K20" t="n">
+        <v>11.67166666666667</v>
+      </c>
+      <c r="L20" t="b">
+        <v>1</v>
+      </c>
+      <c r="M20" t="n">
+        <v>11.60524413625615</v>
+      </c>
+      <c r="N20" t="n">
+        <v>2</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0.06642253041052015</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>0.09999999999999964</v>
+      </c>
+      <c r="R20" t="b">
+        <v>0</v>
+      </c>
+      <c r="S20" t="n">
+        <v>2</v>
+      </c>
+      <c r="T20" t="n">
+        <v>0.04391438782475277</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0</v>
+      </c>
+      <c r="V20" t="n">
+        <v>0.09999999999999964</v>
+      </c>
+      <c r="W20" t="b">
+        <v>0</v>
+      </c>
+      <c r="X20" t="n">
+        <v>11.77693206064009</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>0.1716879243839351</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>estimulados</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>1</v>
+      </c>
+      <c r="D21" t="n">
+        <v>440</v>
+      </c>
+      <c r="E21" t="n">
+        <v>14.93833333333333</v>
+      </c>
+      <c r="F21" t="n">
+        <v>6.993899999999996</v>
+      </c>
+      <c r="G21" t="n">
+        <v>294.2013271098332</v>
+      </c>
+      <c r="H21" t="n">
+        <v>2.377249643537124</v>
+      </c>
+      <c r="I21" t="n">
+        <v>1</v>
+      </c>
+      <c r="J21" t="n">
+        <v>440</v>
+      </c>
+      <c r="K21" t="n">
+        <v>14.93833333333333</v>
+      </c>
+      <c r="L21" t="b">
+        <v>0</v>
+      </c>
+      <c r="M21" t="n">
+        <v>14.87483939589281</v>
+      </c>
+      <c r="N21" t="n">
+        <v>2</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0.06349393744052101</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>0.09999999999999964</v>
+      </c>
+      <c r="R21" t="b">
+        <v>0</v>
+      </c>
+      <c r="S21" t="n">
+        <v>2</v>
+      </c>
+      <c r="T21" t="n">
+        <v>0.06385769271328279</v>
+      </c>
+      <c r="U21" t="n">
+        <v>0</v>
+      </c>
+      <c r="V21" t="n">
+        <v>0.1066666666666709</v>
+      </c>
+      <c r="W21" t="b">
+        <v>0</v>
+      </c>
+      <c r="X21" t="n">
+        <v>15.06080248463021</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>0.1859630887374042</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>espontaneos</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>0</v>
+      </c>
+      <c r="D22" t="n">
+        <v>450</v>
+      </c>
+      <c r="E22" t="n">
+        <v>15.27833333333333</v>
+      </c>
+      <c r="F22" t="n">
+        <v>1.662700000000029</v>
+      </c>
+      <c r="G22" t="n">
+        <v>294.156462528554</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0.5652434033600842</v>
+      </c>
+      <c r="I22" t="n">
+        <v>1</v>
+      </c>
+      <c r="J22" t="n">
+        <v>450</v>
+      </c>
+      <c r="K22" t="n">
+        <v>15.27833333333333</v>
+      </c>
+      <c r="L22" t="b">
+        <v>1</v>
+      </c>
+      <c r="M22" t="n">
+        <v>15.21000861528822</v>
+      </c>
+      <c r="N22" t="n">
+        <v>2</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0.06832471804511009</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>0.09833333333332916</v>
+      </c>
+      <c r="R22" t="b">
+        <v>0</v>
+      </c>
+      <c r="S22" t="n">
+        <v>2</v>
+      </c>
+      <c r="T22" t="n">
+        <v>0.03594812742143461</v>
+      </c>
+      <c r="U22" t="n">
+        <v>0</v>
+      </c>
+      <c r="V22" t="n">
+        <v>0.1016666666666595</v>
+      </c>
+      <c r="W22" t="b">
+        <v>0</v>
+      </c>
+      <c r="X22" t="n">
+        <v>15.35982679647658</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>0.1498181811883619</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>espontaneos</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D23" t="n">
+        <v>458</v>
+      </c>
+      <c r="E23" t="n">
+        <v>15.55</v>
+      </c>
+      <c r="F23" t="n">
+        <v>1.886000000000024</v>
+      </c>
+      <c r="G23" t="n">
+        <v>294.1186033098033</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.6412379151731004</v>
+      </c>
+      <c r="I23" t="n">
+        <v>1</v>
+      </c>
+      <c r="J23" t="n">
+        <v>458</v>
+      </c>
+      <c r="K23" t="n">
+        <v>15.55</v>
+      </c>
+      <c r="L23" t="b">
+        <v>1</v>
+      </c>
+      <c r="M23" t="n">
+        <v>15.47975843239103</v>
+      </c>
+      <c r="N23" t="n">
+        <v>2</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0.07024156760896716</v>
+      </c>
+      <c r="P23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>0.09999999999999964</v>
+      </c>
+      <c r="R23" t="b">
+        <v>0</v>
+      </c>
+      <c r="S23" t="n">
+        <v>2</v>
+      </c>
+      <c r="T23" t="n">
+        <v>0.03859905521109752</v>
+      </c>
+      <c r="U23" t="n">
+        <v>0</v>
+      </c>
+      <c r="V23" t="n">
+        <v>0.09333333333333016</v>
+      </c>
+      <c r="W23" t="b">
+        <v>0</v>
+      </c>
+      <c r="X23" t="n">
+        <v>15.62125419354839</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>0.1414957611573548</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>espontaneos</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>0</v>
+      </c>
+      <c r="D24" t="n">
+        <v>467</v>
+      </c>
+      <c r="E24" t="n">
+        <v>15.83833333333333</v>
+      </c>
+      <c r="F24" t="n">
+        <v>1.691100000000006</v>
+      </c>
+      <c r="G24" t="n">
+        <v>294.1159046764793</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.5749774062236371</v>
+      </c>
+      <c r="I24" t="n">
+        <v>2</v>
+      </c>
+      <c r="J24" t="n">
+        <v>467</v>
+      </c>
+      <c r="K24" t="n">
+        <v>15.83833333333333</v>
+      </c>
+      <c r="L24" t="b">
+        <v>1</v>
+      </c>
+      <c r="M24" t="n">
+        <v>15.76352863317127</v>
+      </c>
+      <c r="N24" t="n">
+        <v>3</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0.07480470016206375</v>
+      </c>
+      <c r="P24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>0.1333333333333293</v>
+      </c>
+      <c r="R24" t="b">
+        <v>0</v>
+      </c>
+      <c r="S24" t="n">
+        <v>2</v>
+      </c>
+      <c r="T24" t="n">
+        <v>0.04981108035675774</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0</v>
+      </c>
+      <c r="V24" t="n">
+        <v>0.1316666666666588</v>
+      </c>
+      <c r="W24" t="b">
+        <v>0</v>
+      </c>
+      <c r="X24" t="n">
+        <v>15.94463069544365</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>0.1811020622723802</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>espontaneos</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>0</v>
+      </c>
+      <c r="D25" t="n">
+        <v>481</v>
+      </c>
+      <c r="E25" t="n">
+        <v>16.305</v>
+      </c>
+      <c r="F25" t="n">
+        <v>1.300000000000011</v>
+      </c>
+      <c r="G25" t="n">
+        <v>294.1511484325548</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.4419496598695365</v>
+      </c>
+      <c r="I25" t="n">
+        <v>2</v>
+      </c>
+      <c r="J25" t="n">
+        <v>481</v>
+      </c>
+      <c r="K25" t="n">
+        <v>16.305</v>
+      </c>
+      <c r="L25" t="b">
+        <v>1</v>
+      </c>
+      <c r="M25" t="n">
+        <v>16.24686112692089</v>
+      </c>
+      <c r="N25" t="n">
+        <v>2</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0.05813887307911259</v>
+      </c>
+      <c r="P25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>0.13333333333334</v>
+      </c>
+      <c r="R25" t="b">
+        <v>0</v>
+      </c>
+      <c r="S25" t="n">
+        <v>3</v>
+      </c>
+      <c r="T25" t="n">
+        <v>0.07519988155167567</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0</v>
+      </c>
+      <c r="V25" t="n">
+        <v>0.1316666666666713</v>
+      </c>
+      <c r="W25" t="b">
+        <v>0</v>
+      </c>
+      <c r="X25" t="n">
+        <v>16.45064314590225</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>0.2037820189813608</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>estimulados</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>1</v>
+      </c>
+      <c r="D26" t="n">
+        <v>740</v>
+      </c>
+      <c r="E26" t="n">
+        <v>24.93666666666667</v>
+      </c>
+      <c r="F26" t="n">
+        <v>7.032300000000021</v>
+      </c>
+      <c r="G26" t="n">
+        <v>294.2397232959302</v>
+      </c>
+      <c r="H26" t="n">
+        <v>2.389990012642623</v>
+      </c>
+      <c r="I26" t="n">
+        <v>1</v>
+      </c>
+      <c r="J26" t="n">
+        <v>740</v>
+      </c>
+      <c r="K26" t="n">
+        <v>24.93666666666667</v>
+      </c>
+      <c r="L26" t="b">
+        <v>0</v>
+      </c>
+      <c r="M26" t="n">
+        <v>24.87587979664488</v>
+      </c>
+      <c r="N26" t="n">
+        <v>2</v>
+      </c>
+      <c r="O26" t="n">
+        <v>0.06078687002178995</v>
+      </c>
+      <c r="P26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>0.1016666666666701</v>
+      </c>
+      <c r="R26" t="b">
+        <v>0</v>
+      </c>
+      <c r="S26" t="n">
+        <v>2</v>
+      </c>
+      <c r="T26" t="n">
+        <v>0.05946369636963311</v>
+      </c>
+      <c r="U26" t="n">
+        <v>0</v>
+      </c>
+      <c r="V26" t="n">
+        <v>0.09833333333332916</v>
+      </c>
+      <c r="W26" t="b">
+        <v>0</v>
+      </c>
+      <c r="X26" t="n">
+        <v>25.06408252781716</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>0.1882027311722823</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>estimulados</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>1</v>
+      </c>
+      <c r="D27" t="n">
+        <v>1040</v>
+      </c>
+      <c r="E27" t="n">
+        <v>34.93666666666667</v>
+      </c>
+      <c r="F27" t="n">
+        <v>6.870100000000036</v>
+      </c>
+      <c r="G27" t="n">
+        <v>294.1919757127387</v>
+      </c>
+      <c r="H27" t="n">
+        <v>2.335243843193156</v>
+      </c>
+      <c r="I27" t="n">
+        <v>1</v>
+      </c>
+      <c r="J27" t="n">
+        <v>1040</v>
+      </c>
+      <c r="K27" t="n">
+        <v>34.93666666666667</v>
+      </c>
+      <c r="L27" t="b">
+        <v>0</v>
+      </c>
+      <c r="M27" t="n">
+        <v>34.87568189346437</v>
+      </c>
+      <c r="N27" t="n">
+        <v>2</v>
+      </c>
+      <c r="O27" t="n">
+        <v>0.06098477320229989</v>
+      </c>
+      <c r="P27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>0.09833333333332916</v>
+      </c>
+      <c r="R27" t="b">
+        <v>0</v>
+      </c>
+      <c r="S27" t="n">
+        <v>2</v>
+      </c>
+      <c r="T27" t="n">
+        <v>0.06340293333334301</v>
+      </c>
+      <c r="U27" t="n">
+        <v>0</v>
+      </c>
+      <c r="V27" t="n">
+        <v>0.1033333333333388</v>
+      </c>
+      <c r="W27" t="b">
+        <v>0</v>
+      </c>
+      <c r="X27" t="n">
+        <v>35.0598166372722</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>0.1841347438078316</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>estimulados</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>1</v>
+      </c>
+      <c r="D28" t="n">
+        <v>1340</v>
+      </c>
+      <c r="E28" t="n">
+        <v>44.94333333333334</v>
+      </c>
+      <c r="F28" t="n">
+        <v>6.675000000000011</v>
+      </c>
+      <c r="G28" t="n">
+        <v>294.1677991825379</v>
+      </c>
+      <c r="H28" t="n">
+        <v>2.269113077144796</v>
+      </c>
+      <c r="I28" t="n">
+        <v>1</v>
+      </c>
+      <c r="J28" t="n">
+        <v>1340</v>
+      </c>
+      <c r="K28" t="n">
+        <v>44.94333333333334</v>
+      </c>
+      <c r="L28" t="b">
+        <v>0</v>
+      </c>
+      <c r="M28" t="n">
+        <v>44.87580165150298</v>
+      </c>
+      <c r="N28" t="n">
+        <v>2</v>
+      </c>
+      <c r="O28" t="n">
+        <v>0.06753168183035996</v>
+      </c>
+      <c r="P28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>0.1049999999999969</v>
+      </c>
+      <c r="R28" t="b">
+        <v>0</v>
+      </c>
+      <c r="S28" t="n">
+        <v>2</v>
+      </c>
+      <c r="T28" t="n">
+        <v>0.05389935763220421</v>
+      </c>
+      <c r="U28" t="n">
+        <v>0</v>
+      </c>
+      <c r="V28" t="n">
+        <v>0.09833333333333627</v>
+      </c>
+      <c r="W28" t="b">
+        <v>0</v>
+      </c>
+      <c r="X28" t="n">
+        <v>45.06119392119393</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>0.1853922696909436</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>estimulados</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>1</v>
+      </c>
+      <c r="D29" t="n">
+        <v>1640</v>
+      </c>
+      <c r="E29" t="n">
+        <v>54.93666666666667</v>
+      </c>
+      <c r="F29" t="n">
+        <v>6.613</v>
+      </c>
+      <c r="G29" t="n">
+        <v>294.1908725605803</v>
+      </c>
+      <c r="H29" t="n">
+        <v>2.247860357611278</v>
+      </c>
+      <c r="I29" t="n">
+        <v>1</v>
+      </c>
+      <c r="J29" t="n">
+        <v>1640</v>
+      </c>
+      <c r="K29" t="n">
+        <v>54.93666666666667</v>
+      </c>
+      <c r="L29" t="b">
+        <v>0</v>
+      </c>
+      <c r="M29" t="n">
+        <v>54.87984217671682</v>
+      </c>
+      <c r="N29" t="n">
+        <v>2</v>
+      </c>
+      <c r="O29" t="n">
+        <v>0.05682448994984668</v>
+      </c>
+      <c r="P29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>0.1016666666666666</v>
+      </c>
+      <c r="R29" t="b">
+        <v>0</v>
+      </c>
+      <c r="S29" t="n">
+        <v>2</v>
+      </c>
+      <c r="T29" t="n">
+        <v>0.06207670532109688</v>
+      </c>
+      <c r="U29" t="n">
+        <v>0</v>
+      </c>
+      <c r="V29" t="n">
+        <v>0.1000000000000014</v>
+      </c>
+      <c r="W29" t="b">
+        <v>0</v>
+      </c>
+      <c r="X29" t="n">
+        <v>55.06085729759004</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>0.1810151208732194</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>estimulados</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>1</v>
+      </c>
+      <c r="D30" t="n">
+        <v>1940</v>
+      </c>
+      <c r="E30" t="n">
+        <v>64.94</v>
+      </c>
+      <c r="F30" t="n">
+        <v>6.744799999999998</v>
+      </c>
+      <c r="G30" t="n">
+        <v>294.1102572478562</v>
+      </c>
+      <c r="H30" t="n">
+        <v>2.293289619721062</v>
+      </c>
+      <c r="I30" t="n">
+        <v>1</v>
+      </c>
+      <c r="J30" t="n">
+        <v>1940</v>
+      </c>
+      <c r="K30" t="n">
+        <v>64.94</v>
+      </c>
+      <c r="L30" t="b">
+        <v>0</v>
+      </c>
+      <c r="M30" t="n">
+        <v>64.87544567409766</v>
+      </c>
+      <c r="N30" t="n">
+        <v>2</v>
+      </c>
+      <c r="O30" t="n">
+        <v>0.06455432590233556</v>
+      </c>
+      <c r="P30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>0.09833333333332916</v>
+      </c>
+      <c r="R30" t="b">
+        <v>0</v>
+      </c>
+      <c r="S30" t="n">
+        <v>2</v>
+      </c>
+      <c r="T30" t="n">
+        <v>0.05568519369163027</v>
+      </c>
+      <c r="U30" t="n">
+        <v>0</v>
+      </c>
+      <c r="V30" t="n">
+        <v>0.1016666666666595</v>
+      </c>
+      <c r="W30" t="b">
+        <v>0</v>
+      </c>
+      <c r="X30" t="n">
+        <v>65.05270866845399</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>0.177262994356326</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:Z4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>grupo</t>
+        </is>
+      </c>
       <c r="B1" t="inlineStr">
         <is>
           <t>cinetica_min_frames</t>
@@ -811,90 +3336,105 @@
       </c>
       <c r="F1" t="inlineStr">
         <is>
+          <t>amplitud_relativa_ic95_pct</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
           <t>amplitud_px</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>ttp_n_eventos</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>ttp_n_medibles</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>ttp_frames_mediana</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>ttp_reportable</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>ttp_s</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>ttp_iqr_s</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>ttp_ic95_s</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
         <is>
           <t>ttp_cota_inf_s</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>ttp_cota_sup_s</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>rt50_n_eventos</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>rt50_n_medibles</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>rt50_frames_mediana</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>rt50_reportable</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>rt50_s</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>rt50_iqr_s</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>rt50_ic95_s</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
         <is>
           <t>rt50_cota_inf_s</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>rt50_cota_sup_s</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>cinetica_motivo</t>
         </is>
@@ -920,50 +3460,57 @@
           <t>0.6809-0.8083</t>
         </is>
       </c>
-      <c r="F2" t="n">
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>0.6931-0.7946</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
         <v>2.093700000000013</v>
       </c>
-      <c r="G2" t="n">
+      <c r="H2" t="n">
         <v>29</v>
       </c>
-      <c r="H2" t="n">
-        <v>0</v>
-      </c>
       <c r="I2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J2" t="b">
-        <v>0</v>
-      </c>
-      <c r="K2" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="J2" t="n">
+        <v>2</v>
+      </c>
+      <c r="K2" t="b">
+        <v>0</v>
+      </c>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N2" t="n">
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P2" t="n">
         <v>0.1016666666666666</v>
       </c>
-      <c r="O2" t="n">
+      <c r="Q2" t="n">
         <v>29</v>
       </c>
-      <c r="P2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>2</v>
-      </c>
-      <c r="R2" t="b">
-        <v>0</v>
-      </c>
-      <c r="S2" t="inlineStr"/>
-      <c r="T2" t="inlineStr"/>
-      <c r="U2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V2" t="n">
+      <c r="R2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S2" t="n">
+        <v>2</v>
+      </c>
+      <c r="T2" t="b">
+        <v>0</v>
+      </c>
+      <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" t="inlineStr"/>
+      <c r="X2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y2" t="n">
         <v>0.1016666666666683</v>
       </c>
-      <c r="W2" t="inlineStr">
+      <c r="Z2" t="inlineStr">
         <is>
           <t>TTP: medible en 0 de 29 eventos (&lt; la mitad con &gt;= 5 fotogramas); solo cota TTP &lt; 102 ms; RT50: medible en 0 de 29 eventos (&lt; la mitad con &gt;= 5 fotogramas); solo cota RT50 &lt; 102 ms</t>
         </is>
@@ -989,50 +3536,57 @@
           <t>2.275-2.367</t>
         </is>
       </c>
-      <c r="F3" t="n">
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>2.258-2.384</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
         <v>6.807450000000017</v>
       </c>
-      <c r="G3" t="n">
+      <c r="H3" t="n">
         <v>6</v>
       </c>
-      <c r="H3" t="n">
-        <v>0</v>
-      </c>
       <c r="I3" t="n">
-        <v>2</v>
-      </c>
-      <c r="J3" t="b">
-        <v>0</v>
-      </c>
-      <c r="K3" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="J3" t="n">
+        <v>2</v>
+      </c>
+      <c r="K3" t="b">
+        <v>0</v>
+      </c>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N3" t="n">
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P3" t="n">
         <v>0.1008333333333331</v>
       </c>
-      <c r="O3" t="n">
+      <c r="Q3" t="n">
         <v>6</v>
       </c>
-      <c r="P3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>2</v>
-      </c>
-      <c r="R3" t="b">
-        <v>0</v>
-      </c>
-      <c r="S3" t="inlineStr"/>
-      <c r="T3" t="inlineStr"/>
-      <c r="U3" t="n">
-        <v>0</v>
-      </c>
-      <c r="V3" t="n">
+      <c r="R3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S3" t="n">
+        <v>2</v>
+      </c>
+      <c r="T3" t="b">
+        <v>0</v>
+      </c>
+      <c r="U3" t="inlineStr"/>
+      <c r="V3" t="inlineStr"/>
+      <c r="W3" t="inlineStr"/>
+      <c r="X3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y3" t="n">
         <v>0.1008333333333304</v>
       </c>
-      <c r="W3" t="inlineStr">
+      <c r="Z3" t="inlineStr">
         <is>
           <t>TTP: medible en 0 de 6 eventos (&lt; la mitad con &gt;= 5 fotogramas); solo cota TTP &lt; 101 ms; RT50: medible en 0 de 6 eventos (&lt; la mitad con &gt;= 5 fotogramas); solo cota RT50 &lt; 101 ms</t>
         </is>
@@ -1058,50 +3612,57 @@
           <t>0.6588-0.7231</t>
         </is>
       </c>
-      <c r="F4" t="n">
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>0.6809-0.722</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
         <v>2.07185000000004</v>
       </c>
-      <c r="G4" t="n">
+      <c r="H4" t="n">
         <v>23</v>
       </c>
-      <c r="H4" t="n">
-        <v>0</v>
-      </c>
       <c r="I4" t="n">
-        <v>2</v>
-      </c>
-      <c r="J4" t="b">
-        <v>0</v>
-      </c>
-      <c r="K4" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="J4" t="n">
+        <v>2</v>
+      </c>
+      <c r="K4" t="b">
+        <v>0</v>
+      </c>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N4" t="n">
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" t="n">
         <v>0.1016666666666666</v>
       </c>
-      <c r="O4" t="n">
+      <c r="Q4" t="n">
         <v>23</v>
       </c>
-      <c r="P4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>2</v>
-      </c>
-      <c r="R4" t="b">
-        <v>0</v>
-      </c>
-      <c r="S4" t="inlineStr"/>
-      <c r="T4" t="inlineStr"/>
-      <c r="U4" t="n">
-        <v>0</v>
-      </c>
-      <c r="V4" t="n">
+      <c r="R4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" t="n">
+        <v>2</v>
+      </c>
+      <c r="T4" t="b">
+        <v>0</v>
+      </c>
+      <c r="U4" t="inlineStr"/>
+      <c r="V4" t="inlineStr"/>
+      <c r="W4" t="inlineStr"/>
+      <c r="X4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y4" t="n">
         <v>0.1033333333333335</v>
       </c>
-      <c r="W4" t="inlineStr">
+      <c r="Z4" t="inlineStr">
         <is>
           <t>TTP: medible en 0 de 23 eventos (&lt; la mitad con &gt;= 5 fotogramas); solo cota TTP &lt; 102 ms; RT50: medible en 0 de 23 eventos (&lt; la mitad con &gt;= 5 fotogramas); solo cota RT50 &lt; 103 ms</t>
         </is>
@@ -1118,7 +3679,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BM2"/>
+  <dimension ref="A1:CC2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1284,167 +3845,247 @@
       </c>
       <c r="AG1" t="inlineStr">
         <is>
+          <t>amplitud_relativa_ic95_pct</t>
+        </is>
+      </c>
+      <c r="AH1" t="inlineStr">
+        <is>
           <t>amplitud_px</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>ttp_n_eventos</t>
         </is>
       </c>
-      <c r="AI1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>ttp_n_medibles</t>
         </is>
       </c>
-      <c r="AJ1" t="inlineStr">
+      <c r="AK1" t="inlineStr">
         <is>
           <t>ttp_frames_mediana</t>
         </is>
       </c>
-      <c r="AK1" t="inlineStr">
+      <c r="AL1" t="inlineStr">
         <is>
           <t>ttp_reportable</t>
         </is>
       </c>
-      <c r="AL1" t="inlineStr">
+      <c r="AM1" t="inlineStr">
         <is>
           <t>ttp_s</t>
         </is>
       </c>
-      <c r="AM1" t="inlineStr">
+      <c r="AN1" t="inlineStr">
         <is>
           <t>ttp_iqr_s</t>
         </is>
       </c>
-      <c r="AN1" t="inlineStr">
+      <c r="AO1" t="inlineStr">
+        <is>
+          <t>ttp_ic95_s</t>
+        </is>
+      </c>
+      <c r="AP1" t="inlineStr">
         <is>
           <t>ttp_cota_inf_s</t>
         </is>
       </c>
-      <c r="AO1" t="inlineStr">
+      <c r="AQ1" t="inlineStr">
         <is>
           <t>ttp_cota_sup_s</t>
         </is>
       </c>
-      <c r="AP1" t="inlineStr">
+      <c r="AR1" t="inlineStr">
         <is>
           <t>rt50_n_eventos</t>
         </is>
       </c>
-      <c r="AQ1" t="inlineStr">
+      <c r="AS1" t="inlineStr">
         <is>
           <t>rt50_n_medibles</t>
         </is>
       </c>
-      <c r="AR1" t="inlineStr">
+      <c r="AT1" t="inlineStr">
         <is>
           <t>rt50_frames_mediana</t>
         </is>
       </c>
-      <c r="AS1" t="inlineStr">
+      <c r="AU1" t="inlineStr">
         <is>
           <t>rt50_reportable</t>
         </is>
       </c>
-      <c r="AT1" t="inlineStr">
+      <c r="AV1" t="inlineStr">
         <is>
           <t>rt50_s</t>
         </is>
       </c>
-      <c r="AU1" t="inlineStr">
+      <c r="AW1" t="inlineStr">
         <is>
           <t>rt50_iqr_s</t>
         </is>
       </c>
-      <c r="AV1" t="inlineStr">
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>rt50_ic95_s</t>
+        </is>
+      </c>
+      <c r="AY1" t="inlineStr">
         <is>
           <t>rt50_cota_inf_s</t>
         </is>
       </c>
-      <c r="AW1" t="inlineStr">
+      <c r="AZ1" t="inlineStr">
         <is>
           <t>rt50_cota_sup_s</t>
         </is>
       </c>
-      <c r="AX1" t="inlineStr">
+      <c r="BA1" t="inlineStr">
         <is>
           <t>cinetica_motivo</t>
         </is>
       </c>
-      <c r="AY1" t="inlineStr">
+      <c r="BB1" t="inlineStr">
         <is>
           <t>fotogramas_sin_medida</t>
         </is>
       </c>
-      <c r="AZ1" t="inlineStr">
+      <c r="BC1" t="inlineStr">
         <is>
           <t>fotogramas_sin_medida_pct</t>
         </is>
       </c>
-      <c r="BA1" t="inlineStr">
+      <c r="BD1" t="inlineStr">
         <is>
           <t>fotogramas_low_quality</t>
         </is>
       </c>
-      <c r="BB1" t="inlineStr">
+      <c r="BE1" t="inlineStr">
         <is>
           <t>eventos_junto_a_hueco</t>
         </is>
       </c>
-      <c r="BC1" t="inlineStr">
+      <c r="BF1" t="inlineStr">
         <is>
           <t>eventos_junto_al_borde</t>
         </is>
       </c>
-      <c r="BD1" t="inlineStr">
+      <c r="BG1" t="inlineStr">
         <is>
           <t>win_s_usado</t>
         </is>
       </c>
-      <c r="BE1" t="inlineStr">
+      <c r="BH1" t="inlineStr">
         <is>
           <t>win_s_automatico</t>
         </is>
       </c>
-      <c r="BF1" t="inlineStr">
+      <c r="BI1" t="inlineStr">
         <is>
           <t>duracion_evento_max_s</t>
         </is>
       </c>
-      <c r="BG1" t="inlineStr">
+      <c r="BJ1" t="inlineStr">
         <is>
           <t>ventana_corta</t>
         </is>
       </c>
-      <c r="BH1" t="inlineStr">
+      <c r="BK1" t="inlineStr">
         <is>
           <t>conteo_por_ventana</t>
         </is>
       </c>
-      <c r="BI1" t="inlineStr">
+      <c r="BL1" t="inlineStr">
         <is>
           <t>conteo_estable_ventana</t>
         </is>
       </c>
-      <c r="BJ1" t="inlineStr">
+      <c r="BM1" t="inlineStr">
         <is>
           <t>mesetas</t>
         </is>
       </c>
-      <c r="BK1" t="inlineStr">
+      <c r="BN1" t="inlineStr">
         <is>
           <t>ruido_borde_sup_px</t>
         </is>
       </c>
-      <c r="BL1" t="inlineStr">
+      <c r="BO1" t="inlineStr">
         <is>
           <t>ruido_borde_inf_px</t>
         </is>
       </c>
-      <c r="BM1" t="inlineStr">
+      <c r="BP1" t="inlineStr">
         <is>
           <t>cociente_ruido_bordes</t>
+        </is>
+      </c>
+      <c r="BQ1" t="inlineStr">
+        <is>
+          <t>basal_fin_s</t>
+        </is>
+      </c>
+      <c r="BR1" t="inlineStr">
+        <is>
+          <t>basal_definicion</t>
+        </is>
+      </c>
+      <c r="BS1" t="inlineStr">
+        <is>
+          <t>basal_actividad_p95_px</t>
+        </is>
+      </c>
+      <c r="BT1" t="inlineStr">
+        <is>
+          <t>basal_actividad_p95_pct</t>
+        </is>
+      </c>
+      <c r="BU1" t="inlineStr">
+        <is>
+          <t>basal_contable</t>
+        </is>
+      </c>
+      <c r="BV1" t="inlineStr">
+        <is>
+          <t>basal_n_contracciones</t>
+        </is>
+      </c>
+      <c r="BW1" t="inlineStr">
+        <is>
+          <t>basal_instantes_s</t>
+        </is>
+      </c>
+      <c r="BX1" t="inlineStr">
+        <is>
+          <t>basal_junto_al_borde</t>
+        </is>
+      </c>
+      <c r="BY1" t="inlineStr">
+        <is>
+          <t>basal_amplitud_mediana_pct</t>
+        </is>
+      </c>
+      <c r="BZ1" t="inlineStr">
+        <is>
+          <t>basal_amplitud_mediana_px</t>
+        </is>
+      </c>
+      <c r="CA1" t="inlineStr">
+        <is>
+          <t>basal_frecuencia_mediana_Hz</t>
+        </is>
+      </c>
+      <c r="CB1" t="inlineStr">
+        <is>
+          <t>basal_frecuencia_iqr_Hz</t>
+        </is>
+      </c>
+      <c r="CC1" t="inlineStr">
+        <is>
+          <t>basal_resumen</t>
         </is>
       </c>
     </row>
@@ -1519,9 +4160,9 @@
        'estimulados', 'estimulados', 'estimulados', 'estimulados',
        'estimulados'], dtype=object), 'tren_por_evento': array([0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 1, 0, 0,
        0, 0, 1, 1, 1, 1, 1]), 'estimulados': array([19, 24, 25, 26, 27, 28]), 'estimulados_dudosos': array([], dtype=int64), 'espontaneos': array([ 0,  1,  2,  3,  4,  5,  6,  7,  8,  9, 10, 11, 12, 13, 14, 15, 16,
-       17, 18, 20, 21, 22, 23]), 'hay_estimulacion': True, 'n_trenes_estimulados': 1, 'tren_principal': 1, 'veredicto': 'enganchado a la frecuencia configurada (0.1 Hz)', 'z': 17.248, 'p_valor': 0.000999000999000999, 'periodo_grilla_s': 9.9682, 'periodo_s': 10.00043, 'periodo_err_s': 0.0023, 'frecuencia_Hz': 0.1, 'frecuencia_err_Hz': 2.3e-05, 'jitter_s': np.float64(0.00962), 'tolerancia_s': 0.0667, 'n_estimulados': 6, 'n_ranuras': 6, 'tasa_captura_pct': 100.0, 'tren_inicio_s': 14.875, 'tren_fin_s': 64.875, 'jitter_limitado_por_resolucion': True, 'resumen_grupos':          grupo   n  t_inicio_s  ...  CV_intervalo_pct  amplitud_mediana_px  amplitud_IQR_px
-0  estimulados   6       14.87  ...               0.0               6.8075           0.2705
-1  espontaneos  23        0.28  ...              90.6               2.0719           0.1889
+       17, 18, 20, 21, 22, 23]), 'hay_estimulacion': True, 'n_trenes_estimulados': 1, 'tren_principal': 1, 'veredicto': 'enganchado a la frecuencia configurada (0.1 Hz)', 'z': 17.248, 'p_valor': 0.000999000999000999, 'periodo_grilla_s': 9.9682, 'periodo_s': 10.00043, 'periodo_err_s': 0.0023, 'frecuencia_Hz': 0.1, 'frecuencia_err_Hz': 2.3e-05, 'jitter_s': np.float64(0.00962), 'tolerancia_s': 0.0667, 'n_estimulados': 6, 'n_ranuras': 6, 'tasa_captura_pct': 100.0, 'tren_inicio_s': 14.875, 'tren_fin_s': 64.875, 'jitter_limitado_por_resolucion': True, 'resumen_grupos':          grupo   n  ...  amplitud_mediana_px  amplitud_IQR_px
+0  estimulados   6  ...               6.8075           0.2705
+1  espontaneos  23  ...               2.0719           0.1889
 [2 rows x 10 columns], 'espontaneas_instantanea':     tiempo_s  intervalo_s  frecuencia_Hz
 0      0.569       0.5813         1.7204
 1      1.139       0.5593         1.7880
@@ -1602,102 +4243,156 @@
           <t>2.275-2.367</t>
         </is>
       </c>
-      <c r="AG2" t="n">
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>2.258-2.384</t>
+        </is>
+      </c>
+      <c r="AH2" t="n">
         <v>6.807450000000017</v>
       </c>
-      <c r="AH2" t="n">
+      <c r="AI2" t="n">
         <v>6</v>
       </c>
-      <c r="AI2" t="n">
-        <v>0</v>
-      </c>
       <c r="AJ2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AK2" t="b">
-        <v>0</v>
-      </c>
-      <c r="AL2" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL2" t="b">
+        <v>0</v>
+      </c>
       <c r="AM2" t="inlineStr"/>
-      <c r="AN2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO2" t="n">
+      <c r="AN2" t="inlineStr"/>
+      <c r="AO2" t="inlineStr"/>
+      <c r="AP2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ2" t="n">
         <v>0.1008333333333331</v>
       </c>
-      <c r="AP2" t="n">
+      <c r="AR2" t="n">
         <v>6</v>
       </c>
-      <c r="AQ2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AS2" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT2" t="inlineStr"/>
-      <c r="AU2" t="inlineStr"/>
-      <c r="AV2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW2" t="n">
+      <c r="AS2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AV2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr"/>
+      <c r="AX2" t="inlineStr"/>
+      <c r="AY2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ2" t="n">
         <v>0.1008333333333304</v>
       </c>
-      <c r="AX2" t="inlineStr">
+      <c r="BA2" t="inlineStr">
         <is>
           <t>TTP: medible en 0 de 6 eventos (&lt; la mitad con &gt;= 5 fotogramas); solo cota TTP &lt; 101 ms; RT50: medible en 0 de 6 eventos (&lt; la mitad con &gt;= 5 fotogramas); solo cota RT50 &lt; 101 ms</t>
         </is>
       </c>
-      <c r="AY2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>0</v>
-      </c>
       <c r="BB2" t="n">
         <v>0</v>
       </c>
       <c r="BC2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BD2" t="n">
-        <v>2</v>
-      </c>
-      <c r="BE2" t="b">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>0</v>
       </c>
       <c r="BF2" t="n">
+        <v>2</v>
+      </c>
+      <c r="BG2" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH2" t="b">
+        <v>1</v>
+      </c>
+      <c r="BI2" t="n">
         <v>0.2333333333333201</v>
       </c>
-      <c r="BG2" t="b">
-        <v>0</v>
-      </c>
-      <c r="BH2" t="inlineStr">
+      <c r="BJ2" t="b">
+        <v>0</v>
+      </c>
+      <c r="BK2" t="inlineStr">
         <is>
           <t>1.5 s: 29 | 2 s: 29 | 3 s: 29</t>
         </is>
       </c>
-      <c r="BI2" t="b">
-        <v>1</v>
-      </c>
-      <c r="BJ2" t="inlineStr">
+      <c r="BL2" t="b">
+        <v>1</v>
+      </c>
+      <c r="BM2" t="inlineStr">
         <is>
           <t>29 ev en k=5.315-15.163</t>
         </is>
       </c>
-      <c r="BK2" t="n">
+      <c r="BN2" t="n">
         <v>0.1095641400000554</v>
       </c>
-      <c r="BL2" t="n">
+      <c r="BO2" t="n">
         <v>0.08569428000006364</v>
       </c>
-      <c r="BM2" t="n">
+      <c r="BP2" t="n">
         <v>1.278546712802465</v>
+      </c>
+      <c r="BQ2" t="n">
+        <v>10</v>
+      </c>
+      <c r="BR2" t="inlineStr">
+        <is>
+          <t>0-10 s</t>
+        </is>
+      </c>
+      <c r="BS2" t="n">
+        <v>1.978114999999999</v>
+      </c>
+      <c r="BT2" t="n">
+        <v>0.6723889238758761</v>
+      </c>
+      <c r="BU2" t="b">
+        <v>1</v>
+      </c>
+      <c r="BV2" t="n">
+        <v>17</v>
+      </c>
+      <c r="BW2" t="inlineStr">
+        <is>
+          <t>0.34, 0.91, 1.47, 2.04, 2.60, 3.17, 3.74, 4.31, 4.87, 5.45, 5.97, 6.57, 7.28, 7.67, 8.28, 9.34, 9.94</t>
+        </is>
+      </c>
+      <c r="BX2" t="n">
+        <v>2</v>
+      </c>
+      <c r="BY2" t="n">
+        <v>0.7080886589006981</v>
+      </c>
+      <c r="BZ2" t="n">
+        <v>2.083199999999977</v>
+      </c>
+      <c r="CA2" t="n">
+        <v>1.762118337070897</v>
+      </c>
+      <c r="CB2" t="inlineStr">
+        <is>
+          <t>1.67-1.77</t>
+        </is>
+      </c>
+      <c r="CC2" t="inlineStr">
+        <is>
+          <t>17 contraccion(es) en 10.0 s; amplitud mediana 0.71 %; frecuencia mediana 1.76 Hz (IQR 1.67-1.77); actividad basal 0.67 % del grosor</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -2510,7 +5205,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E30"/>
+  <dimension ref="A1:G30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2539,6 +5234,16 @@
           <t>junto_al_borde</t>
         </is>
       </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>en_promedio</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>reportable</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -2556,6 +5261,12 @@
       <c r="E2" t="b">
         <v>1</v>
       </c>
+      <c r="F2" t="b">
+        <v>0</v>
+      </c>
+      <c r="G2" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -2571,6 +5282,12 @@
         <v>0</v>
       </c>
       <c r="E3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G3" t="b">
         <v>1</v>
       </c>
     </row>
@@ -2590,6 +5307,12 @@
       <c r="E4" t="b">
         <v>0</v>
       </c>
+      <c r="F4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G4" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -2607,6 +5330,12 @@
       <c r="E5" t="b">
         <v>0</v>
       </c>
+      <c r="F5" t="b">
+        <v>1</v>
+      </c>
+      <c r="G5" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -2624,6 +5353,12 @@
       <c r="E6" t="b">
         <v>0</v>
       </c>
+      <c r="F6" t="b">
+        <v>1</v>
+      </c>
+      <c r="G6" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -2641,6 +5376,12 @@
       <c r="E7" t="b">
         <v>0</v>
       </c>
+      <c r="F7" t="b">
+        <v>1</v>
+      </c>
+      <c r="G7" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -2658,6 +5399,12 @@
       <c r="E8" t="b">
         <v>0</v>
       </c>
+      <c r="F8" t="b">
+        <v>1</v>
+      </c>
+      <c r="G8" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -2675,6 +5422,12 @@
       <c r="E9" t="b">
         <v>0</v>
       </c>
+      <c r="F9" t="b">
+        <v>1</v>
+      </c>
+      <c r="G9" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -2692,6 +5445,12 @@
       <c r="E10" t="b">
         <v>0</v>
       </c>
+      <c r="F10" t="b">
+        <v>1</v>
+      </c>
+      <c r="G10" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -2709,6 +5468,12 @@
       <c r="E11" t="b">
         <v>0</v>
       </c>
+      <c r="F11" t="b">
+        <v>1</v>
+      </c>
+      <c r="G11" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -2726,6 +5491,12 @@
       <c r="E12" t="b">
         <v>0</v>
       </c>
+      <c r="F12" t="b">
+        <v>1</v>
+      </c>
+      <c r="G12" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2743,6 +5514,12 @@
       <c r="E13" t="b">
         <v>0</v>
       </c>
+      <c r="F13" t="b">
+        <v>1</v>
+      </c>
+      <c r="G13" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2760,6 +5537,12 @@
       <c r="E14" t="b">
         <v>0</v>
       </c>
+      <c r="F14" t="b">
+        <v>1</v>
+      </c>
+      <c r="G14" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2777,6 +5560,12 @@
       <c r="E15" t="b">
         <v>0</v>
       </c>
+      <c r="F15" t="b">
+        <v>1</v>
+      </c>
+      <c r="G15" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2794,6 +5583,12 @@
       <c r="E16" t="b">
         <v>0</v>
       </c>
+      <c r="F16" t="b">
+        <v>1</v>
+      </c>
+      <c r="G16" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2811,6 +5606,12 @@
       <c r="E17" t="b">
         <v>0</v>
       </c>
+      <c r="F17" t="b">
+        <v>1</v>
+      </c>
+      <c r="G17" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2828,6 +5629,12 @@
       <c r="E18" t="b">
         <v>0</v>
       </c>
+      <c r="F18" t="b">
+        <v>1</v>
+      </c>
+      <c r="G18" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2845,6 +5652,12 @@
       <c r="E19" t="b">
         <v>0</v>
       </c>
+      <c r="F19" t="b">
+        <v>1</v>
+      </c>
+      <c r="G19" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2862,6 +5675,12 @@
       <c r="E20" t="b">
         <v>0</v>
       </c>
+      <c r="F20" t="b">
+        <v>1</v>
+      </c>
+      <c r="G20" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2879,6 +5698,12 @@
       <c r="E21" t="b">
         <v>0</v>
       </c>
+      <c r="F21" t="b">
+        <v>1</v>
+      </c>
+      <c r="G21" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2896,6 +5721,12 @@
       <c r="E22" t="b">
         <v>0</v>
       </c>
+      <c r="F22" t="b">
+        <v>1</v>
+      </c>
+      <c r="G22" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2913,6 +5744,12 @@
       <c r="E23" t="b">
         <v>0</v>
       </c>
+      <c r="F23" t="b">
+        <v>1</v>
+      </c>
+      <c r="G23" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2930,6 +5767,12 @@
       <c r="E24" t="b">
         <v>0</v>
       </c>
+      <c r="F24" t="b">
+        <v>1</v>
+      </c>
+      <c r="G24" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -2947,6 +5790,12 @@
       <c r="E25" t="b">
         <v>0</v>
       </c>
+      <c r="F25" t="b">
+        <v>1</v>
+      </c>
+      <c r="G25" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -2964,6 +5813,12 @@
       <c r="E26" t="b">
         <v>0</v>
       </c>
+      <c r="F26" t="b">
+        <v>1</v>
+      </c>
+      <c r="G26" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -2981,6 +5836,12 @@
       <c r="E27" t="b">
         <v>0</v>
       </c>
+      <c r="F27" t="b">
+        <v>1</v>
+      </c>
+      <c r="G27" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -2998,6 +5859,12 @@
       <c r="E28" t="b">
         <v>0</v>
       </c>
+      <c r="F28" t="b">
+        <v>1</v>
+      </c>
+      <c r="G28" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3015,6 +5882,12 @@
       <c r="E29" t="b">
         <v>0</v>
       </c>
+      <c r="F29" t="b">
+        <v>1</v>
+      </c>
+      <c r="G29" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3031,6 +5904,12 @@
       </c>
       <c r="E30" t="b">
         <v>0</v>
+      </c>
+      <c r="F30" t="b">
+        <v>1</v>
+      </c>
+      <c r="G30" t="b">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -3044,2241 +5923,175 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W30"/>
+  <dimension ref="A1:B14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>evento</t>
+          <t>dato</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>grupo</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>tren</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>frame_pico</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>tiempo_s</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>amplitud_px</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>grosor_reposo_px</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>amplitud_relativa_pct</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>meseta_pico_frames</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>onset_s</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>ttp_frames</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>ttp_s</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>ttp_min_s</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>ttp_max_s</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>ttp_medible</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>rt50_frames</t>
-        </is>
-      </c>
-      <c r="Q1" t="inlineStr">
-        <is>
-          <t>rt50_s</t>
-        </is>
-      </c>
-      <c r="R1" t="inlineStr">
-        <is>
-          <t>rt50_min_s</t>
-        </is>
-      </c>
-      <c r="S1" t="inlineStr">
-        <is>
-          <t>rt50_max_s</t>
-        </is>
-      </c>
-      <c r="T1" t="inlineStr">
-        <is>
-          <t>rt50_medible</t>
-        </is>
-      </c>
-      <c r="U1" t="inlineStr">
-        <is>
-          <t>offset_s</t>
-        </is>
-      </c>
-      <c r="V1" t="inlineStr">
-        <is>
-          <t>duracion_frames</t>
-        </is>
-      </c>
-      <c r="W1" t="inlineStr">
-        <is>
-          <t>duracion_s</t>
+          <t>valor</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
-        <v>1</v>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>basal_fin_s</t>
+        </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>espontaneos</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2" t="n">
-        <v>11</v>
-      </c>
-      <c r="E2" t="n">
-        <v>0.3383333333333334</v>
-      </c>
-      <c r="F2" t="n">
-        <v>2.07185000000004</v>
-      </c>
-      <c r="G2" t="n">
-        <v>294.186442631115</v>
-      </c>
-      <c r="H2" t="n">
-        <v>0.7042642691043263</v>
-      </c>
-      <c r="I2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J2" t="n">
-        <v>0.277989655707567</v>
-      </c>
-      <c r="K2" t="n">
-        <v>2</v>
-      </c>
-      <c r="L2" t="n">
-        <v>0.06034367762576642</v>
-      </c>
-      <c r="M2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N2" t="n">
-        <v>0.09833333333333333</v>
-      </c>
-      <c r="O2" t="b">
-        <v>0</v>
-      </c>
-      <c r="P2" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>0.04847599810750691</v>
-      </c>
-      <c r="R2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S2" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="T2" t="b">
-        <v>0</v>
-      </c>
-      <c r="U2" t="n">
-        <v>0.4330979839398581</v>
-      </c>
-      <c r="V2" t="n">
-        <v>5</v>
-      </c>
-      <c r="W2" t="n">
-        <v>0.1551083282322911</v>
+          <t>10.0</t>
+        </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="n">
-        <v>2</v>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>basal_definicion</t>
+        </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>espontaneos</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D3" t="n">
-        <v>28</v>
-      </c>
-      <c r="E3" t="n">
-        <v>0.91</v>
-      </c>
-      <c r="F3" t="n">
-        <v>1.911099999999976</v>
-      </c>
-      <c r="G3" t="n">
-        <v>294.1858218643114</v>
-      </c>
-      <c r="H3" t="n">
-        <v>0.6496234209687513</v>
-      </c>
-      <c r="I3" t="n">
-        <v>2</v>
-      </c>
-      <c r="J3" t="n">
-        <v>0.8592479658844149</v>
-      </c>
-      <c r="K3" t="n">
-        <v>2</v>
-      </c>
-      <c r="L3" t="n">
-        <v>0.05075203411558515</v>
-      </c>
-      <c r="M3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N3" t="n">
-        <v>0.1333333333333333</v>
-      </c>
-      <c r="O3" t="b">
-        <v>0</v>
-      </c>
-      <c r="P3" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>0.06212855624788582</v>
-      </c>
-      <c r="R3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S3" t="n">
-        <v>0.1416666666666663</v>
-      </c>
-      <c r="T3" t="b">
-        <v>0</v>
-      </c>
-      <c r="U3" t="n">
-        <v>1.032840827980012</v>
-      </c>
-      <c r="V3" t="n">
-        <v>6</v>
-      </c>
-      <c r="W3" t="n">
-        <v>0.1735928620955974</v>
+          <t>0-10 s</t>
+        </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="n">
-        <v>3</v>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>basal_actividad_p95_px</t>
+        </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>espontaneos</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D4" t="n">
-        <v>45</v>
-      </c>
-      <c r="E4" t="n">
-        <v>1.471666666666667</v>
-      </c>
-      <c r="F4" t="n">
-        <v>2.083199999999977</v>
-      </c>
-      <c r="G4" t="n">
-        <v>294.2004470505329</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0.7080886589006981</v>
-      </c>
-      <c r="I4" t="n">
-        <v>1</v>
-      </c>
-      <c r="J4" t="n">
-        <v>1.41853570329332</v>
-      </c>
-      <c r="K4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0.05313096337334677</v>
-      </c>
-      <c r="M4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N4" t="n">
-        <v>0.1083333333333329</v>
-      </c>
-      <c r="O4" t="b">
-        <v>0</v>
-      </c>
-      <c r="P4" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>0.07726777939042195</v>
-      </c>
-      <c r="R4" t="n">
-        <v>0.02500000000000013</v>
-      </c>
-      <c r="S4" t="n">
-        <v>0.133333333333334</v>
-      </c>
-      <c r="T4" t="b">
-        <v>0</v>
-      </c>
-      <c r="U4" t="n">
-        <v>1.598569790012352</v>
-      </c>
-      <c r="V4" t="n">
-        <v>6</v>
-      </c>
-      <c r="W4" t="n">
-        <v>0.180034086719032</v>
+          <t>1.978114999999999</t>
+        </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="n">
-        <v>4</v>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>basal_actividad_p95_pct</t>
+        </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>espontaneos</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D5" t="n">
-        <v>62</v>
-      </c>
-      <c r="E5" t="n">
-        <v>2.038333333333334</v>
-      </c>
-      <c r="F5" t="n">
-        <v>2.518399999999986</v>
-      </c>
-      <c r="G5" t="n">
-        <v>294.2096897179215</v>
-      </c>
-      <c r="H5" t="n">
-        <v>0.8559881227618792</v>
-      </c>
-      <c r="I5" t="n">
-        <v>1</v>
-      </c>
-      <c r="J5" t="n">
-        <v>1.982052650145516</v>
-      </c>
-      <c r="K5" t="n">
-        <v>2</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0.05628068318781798</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0.1000000000000003</v>
-      </c>
-      <c r="O5" t="b">
-        <v>0</v>
-      </c>
-      <c r="P5" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>0.05580770747092556</v>
-      </c>
-      <c r="R5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" t="n">
-        <v>0.09333333333333282</v>
-      </c>
-      <c r="T5" t="b">
-        <v>0</v>
-      </c>
-      <c r="U5" t="n">
-        <v>2.14553618388036</v>
-      </c>
-      <c r="V5" t="n">
-        <v>6</v>
-      </c>
-      <c r="W5" t="n">
-        <v>0.1634835337348437</v>
+          <t>0.6723889238758761</t>
+        </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="n">
-        <v>5</v>
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>basal_contable</t>
+        </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>espontaneos</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>0</v>
-      </c>
-      <c r="D6" t="n">
-        <v>79</v>
-      </c>
-      <c r="E6" t="n">
-        <v>2.605</v>
-      </c>
-      <c r="F6" t="n">
-        <v>2.356300000000033</v>
-      </c>
-      <c r="G6" t="n">
-        <v>294.2180072554886</v>
-      </c>
-      <c r="H6" t="n">
-        <v>0.8008687238350795</v>
-      </c>
-      <c r="I6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J6" t="n">
-        <v>2.553522137404581</v>
-      </c>
-      <c r="K6" t="n">
-        <v>2</v>
-      </c>
-      <c r="L6" t="n">
-        <v>0.05147786259541931</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" t="n">
-        <v>0.09833333333333316</v>
-      </c>
-      <c r="O6" t="b">
-        <v>0</v>
-      </c>
-      <c r="P6" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>0.06237304750793804</v>
-      </c>
-      <c r="R6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S6" t="n">
-        <v>0.1000000000000001</v>
-      </c>
-      <c r="T6" t="b">
-        <v>0</v>
-      </c>
-      <c r="U6" t="n">
-        <v>2.708330000000001</v>
-      </c>
-      <c r="V6" t="n">
-        <v>6</v>
-      </c>
-      <c r="W6" t="n">
-        <v>0.1548078625954203</v>
+          <t>True</t>
+        </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="n">
-        <v>6</v>
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>basal_n_contracciones</t>
+        </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>espontaneos</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>0</v>
-      </c>
-      <c r="D7" t="n">
-        <v>96</v>
-      </c>
-      <c r="E7" t="n">
-        <v>3.171666666666667</v>
-      </c>
-      <c r="F7" t="n">
-        <v>1.922900000000027</v>
-      </c>
-      <c r="G7" t="n">
-        <v>294.2257620822636</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0.6535457624075749</v>
-      </c>
-      <c r="I7" t="n">
-        <v>2</v>
-      </c>
-      <c r="J7" t="n">
-        <v>3.127293428757324</v>
-      </c>
-      <c r="K7" t="n">
-        <v>2</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0.04437323790934311</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0.1333333333333342</v>
-      </c>
-      <c r="O7" t="b">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>0.0682990182060812</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" t="n">
-        <v>0.1333333333333329</v>
-      </c>
-      <c r="T7" t="b">
-        <v>0</v>
-      </c>
-      <c r="U7" t="n">
-        <v>3.281085168239442</v>
-      </c>
-      <c r="V7" t="n">
-        <v>6</v>
-      </c>
-      <c r="W7" t="n">
-        <v>0.1537917394821178</v>
+          <t>17</t>
+        </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="n">
-        <v>7</v>
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>basal_instantes_s</t>
+        </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>espontaneos</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>0</v>
-      </c>
-      <c r="D8" t="n">
-        <v>113</v>
-      </c>
-      <c r="E8" t="n">
-        <v>3.736666666666667</v>
-      </c>
-      <c r="F8" t="n">
-        <v>2.043000000000006</v>
-      </c>
-      <c r="G8" t="n">
-        <v>294.1927371840957</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0.6944427043151535</v>
-      </c>
-      <c r="I8" t="n">
-        <v>1</v>
-      </c>
-      <c r="J8" t="n">
-        <v>3.688532583577262</v>
-      </c>
-      <c r="K8" t="n">
-        <v>2</v>
-      </c>
-      <c r="L8" t="n">
-        <v>0.04813408308940481</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0.105</v>
-      </c>
-      <c r="O8" t="b">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>0.07283428968874883</v>
-      </c>
-      <c r="R8" t="n">
-        <v>0</v>
-      </c>
-      <c r="S8" t="n">
-        <v>0.1083333333333329</v>
-      </c>
-      <c r="T8" t="b">
-        <v>0</v>
-      </c>
-      <c r="U8" t="n">
-        <v>3.845477477477479</v>
-      </c>
-      <c r="V8" t="n">
-        <v>6</v>
-      </c>
-      <c r="W8" t="n">
-        <v>0.1569448939002172</v>
+          <t>0.34, 0.91, 1.47, 2.04, 2.60, 3.17, 3.74, 4.31, 4.87, 5.45, 5.97, 6.57, 7.28, 7.67, 8.28, 9.34, 9.94</t>
+        </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="n">
-        <v>8</v>
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>basal_junto_al_borde</t>
+        </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>espontaneos</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>0</v>
-      </c>
-      <c r="D9" t="n">
-        <v>130</v>
-      </c>
-      <c r="E9" t="n">
-        <v>4.305000000000001</v>
-      </c>
-      <c r="F9" t="n">
-        <v>1.953499999999963</v>
-      </c>
-      <c r="G9" t="n">
-        <v>294.1927371840957</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0.6640204713067168</v>
-      </c>
-      <c r="I9" t="n">
-        <v>2</v>
-      </c>
-      <c r="J9" t="n">
-        <v>4.253494974191794</v>
-      </c>
-      <c r="K9" t="n">
-        <v>2</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0.05150502580820682</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0.1333333333333337</v>
-      </c>
-      <c r="O9" t="b">
-        <v>0</v>
-      </c>
-      <c r="P9" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>0.07340231680333265</v>
-      </c>
-      <c r="R9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S9" t="n">
-        <v>0.1333333333333329</v>
-      </c>
-      <c r="T9" t="b">
-        <v>0</v>
-      </c>
-      <c r="U9" t="n">
-        <v>4.418203921568629</v>
-      </c>
-      <c r="V9" t="n">
-        <v>6</v>
-      </c>
-      <c r="W9" t="n">
-        <v>0.1647089473768348</v>
+          <t>2</t>
+        </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="n">
-        <v>9</v>
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>basal_amplitud_mediana_pct</t>
+        </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>espontaneos</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>0</v>
-      </c>
-      <c r="D10" t="n">
-        <v>147</v>
-      </c>
-      <c r="E10" t="n">
-        <v>4.871666666666667</v>
-      </c>
-      <c r="F10" t="n">
-        <v>2.0976</v>
-      </c>
-      <c r="G10" t="n">
-        <v>294.1914281912709</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0.7130051384897008</v>
-      </c>
-      <c r="I10" t="n">
-        <v>1</v>
-      </c>
-      <c r="J10" t="n">
-        <v>4.817098754578756</v>
-      </c>
-      <c r="K10" t="n">
-        <v>2</v>
-      </c>
-      <c r="L10" t="n">
-        <v>0.05456791208791145</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0.09833333333333272</v>
-      </c>
-      <c r="O10" t="b">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>0.06285318951238228</v>
-      </c>
-      <c r="R10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S10" t="n">
-        <v>0.1016666666666657</v>
-      </c>
-      <c r="T10" t="b">
-        <v>0</v>
-      </c>
-      <c r="U10" t="n">
-        <v>4.980667027221918</v>
-      </c>
-      <c r="V10" t="n">
-        <v>6</v>
-      </c>
-      <c r="W10" t="n">
-        <v>0.163568272643162</v>
+          <t>0.708088658900698</t>
+        </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="n">
-        <v>10</v>
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>basal_amplitud_mediana_px</t>
+        </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>espontaneos</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>0</v>
-      </c>
-      <c r="D11" t="n">
-        <v>164</v>
-      </c>
-      <c r="E11" t="n">
-        <v>5.446666666666667</v>
-      </c>
-      <c r="F11" t="n">
-        <v>2.093700000000013</v>
-      </c>
-      <c r="G11" t="n">
-        <v>294.1920858240017</v>
-      </c>
-      <c r="H11" t="n">
-        <v>0.7116778801631508</v>
-      </c>
-      <c r="I11" t="n">
-        <v>1</v>
-      </c>
-      <c r="J11" t="n">
-        <v>5.378556092306326</v>
-      </c>
-      <c r="K11" t="n">
-        <v>2</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0.0681105743603414</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0.1016666666666666</v>
-      </c>
-      <c r="O11" t="b">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>0.05135885071328072</v>
-      </c>
-      <c r="R11" t="n">
-        <v>0</v>
-      </c>
-      <c r="S11" t="n">
-        <v>0.1133333333333333</v>
-      </c>
-      <c r="T11" t="b">
-        <v>0</v>
-      </c>
-      <c r="U11" t="n">
-        <v>5.586102227298683</v>
-      </c>
-      <c r="V11" t="n">
-        <v>7</v>
-      </c>
-      <c r="W11" t="n">
-        <v>0.2075461349923575</v>
+          <t>2.0831999999999766</t>
+        </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="n">
-        <v>11</v>
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>basal_frecuencia_mediana_Hz</t>
+        </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>espontaneos</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
-        <v>0</v>
-      </c>
-      <c r="D12" t="n">
-        <v>180</v>
-      </c>
-      <c r="E12" t="n">
-        <v>5.971666666666667</v>
-      </c>
-      <c r="F12" t="n">
-        <v>2.081199999999967</v>
-      </c>
-      <c r="G12" t="n">
-        <v>294.1757204680613</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0.7074683106711124</v>
-      </c>
-      <c r="I12" t="n">
-        <v>1</v>
-      </c>
-      <c r="J12" t="n">
-        <v>5.91788425690561</v>
-      </c>
-      <c r="K12" t="n">
-        <v>2</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0.05378240976105708</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" t="n">
-        <v>0.1083333333333334</v>
-      </c>
-      <c r="O12" t="b">
-        <v>0</v>
-      </c>
-      <c r="P12" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>0.07456235663406829</v>
-      </c>
-      <c r="R12" t="n">
-        <v>0.02500000000000036</v>
-      </c>
-      <c r="S12" t="n">
-        <v>0.1333333333333346</v>
-      </c>
-      <c r="T12" t="b">
-        <v>0</v>
-      </c>
-      <c r="U12" t="n">
-        <v>6.099438589379813</v>
-      </c>
-      <c r="V12" t="n">
-        <v>6</v>
-      </c>
-      <c r="W12" t="n">
-        <v>0.1815543324742031</v>
+          <t>1.7621183370708975</t>
+        </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="n">
-        <v>12</v>
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>basal_frecuencia_iqr_Hz</t>
+        </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>espontaneos</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
-        <v>0</v>
-      </c>
-      <c r="D13" t="n">
-        <v>198</v>
-      </c>
-      <c r="E13" t="n">
-        <v>6.571666666666667</v>
-      </c>
-      <c r="F13" t="n">
-        <v>2.378100000000018</v>
-      </c>
-      <c r="G13" t="n">
-        <v>294.2090886717925</v>
-      </c>
-      <c r="H13" t="n">
-        <v>0.8083026974917583</v>
-      </c>
-      <c r="I13" t="n">
-        <v>1</v>
-      </c>
-      <c r="J13" t="n">
-        <v>6.508522902232486</v>
-      </c>
-      <c r="K13" t="n">
-        <v>3</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0.06314376443418102</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0.03000000000000025</v>
-      </c>
-      <c r="N13" t="n">
-        <v>0.1333333333333337</v>
-      </c>
-      <c r="O13" t="b">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>0.04022487482117132</v>
-      </c>
-      <c r="R13" t="n">
-        <v>0</v>
-      </c>
-      <c r="S13" t="n">
-        <v>0.1033333333333335</v>
-      </c>
-      <c r="T13" t="b">
-        <v>0</v>
-      </c>
-      <c r="U13" t="n">
-        <v>6.664180808080808</v>
-      </c>
-      <c r="V13" t="n">
-        <v>6</v>
-      </c>
-      <c r="W13" t="n">
-        <v>0.1556579058483214</v>
+          <t>1.67-1.77</t>
+        </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="n">
-        <v>13</v>
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>basal_resumen</t>
+        </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>espontaneos</t>
-        </is>
-      </c>
-      <c r="C14" t="n">
-        <v>0</v>
-      </c>
-      <c r="D14" t="n">
-        <v>209</v>
-      </c>
-      <c r="E14" t="n">
-        <v>7.28</v>
-      </c>
-      <c r="F14" t="n">
-        <v>2.12360000000001</v>
-      </c>
-      <c r="G14" t="n">
-        <v>294.1229333192731</v>
-      </c>
-      <c r="H14" t="n">
-        <v>0.7220110230897308</v>
-      </c>
-      <c r="I14" t="n">
-        <v>1</v>
-      </c>
-      <c r="J14" t="n">
-        <v>7.265851470196322</v>
-      </c>
-      <c r="K14" t="n">
-        <v>1</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0.01414852980367787</v>
-      </c>
-      <c r="M14" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" t="n">
-        <v>0.03333333333333321</v>
-      </c>
-      <c r="O14" t="b">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>0.008140141061024231</v>
-      </c>
-      <c r="R14" t="n">
-        <v>0</v>
-      </c>
-      <c r="S14" t="n">
-        <v>0.03333333333333321</v>
-      </c>
-      <c r="T14" t="b">
-        <v>0</v>
-      </c>
-      <c r="U14" t="n">
-        <v>7.294652253909844</v>
-      </c>
-      <c r="V14" t="n">
-        <v>2</v>
-      </c>
-      <c r="W14" t="n">
-        <v>0.02880078371352202</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>14</v>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>espontaneos</t>
-        </is>
-      </c>
-      <c r="C15" t="n">
-        <v>0</v>
-      </c>
-      <c r="D15" t="n">
-        <v>222</v>
-      </c>
-      <c r="E15" t="n">
-        <v>7.671666666666667</v>
-      </c>
-      <c r="F15" t="n">
-        <v>2.038999999999987</v>
-      </c>
-      <c r="G15" t="n">
-        <v>294.1707185111845</v>
-      </c>
-      <c r="H15" t="n">
-        <v>0.6931349286970123</v>
-      </c>
-      <c r="I15" t="n">
-        <v>1</v>
-      </c>
-      <c r="J15" t="n">
-        <v>7.610206812652068</v>
-      </c>
-      <c r="K15" t="n">
-        <v>2</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0.06145985401459875</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0.09999999999999964</v>
-      </c>
-      <c r="O15" t="b">
-        <v>0</v>
-      </c>
-      <c r="P15" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>0.06134544667964548</v>
-      </c>
-      <c r="R15" t="n">
-        <v>0</v>
-      </c>
-      <c r="S15" t="n">
-        <v>0.1000000000000005</v>
-      </c>
-      <c r="T15" t="b">
-        <v>0</v>
-      </c>
-      <c r="U15" t="n">
-        <v>7.780480532638585</v>
-      </c>
-      <c r="V15" t="n">
-        <v>6</v>
-      </c>
-      <c r="W15" t="n">
-        <v>0.1702737199865165</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>15</v>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>espontaneos</t>
-        </is>
-      </c>
-      <c r="C16" t="n">
-        <v>0</v>
-      </c>
-      <c r="D16" t="n">
-        <v>240</v>
-      </c>
-      <c r="E16" t="n">
-        <v>8.283333333333333</v>
-      </c>
-      <c r="F16" t="n">
-        <v>2.130499999999984</v>
-      </c>
-      <c r="G16" t="n">
-        <v>294.2228176658223</v>
-      </c>
-      <c r="H16" t="n">
-        <v>0.7241110723165602</v>
-      </c>
-      <c r="I16" t="n">
-        <v>1</v>
-      </c>
-      <c r="J16" t="n">
-        <v>8.206060895395717</v>
-      </c>
-      <c r="K16" t="n">
-        <v>3</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0.07727243793761573</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0.02333333333333165</v>
-      </c>
-      <c r="N16" t="n">
-        <v>0.1316666666666677</v>
-      </c>
-      <c r="O16" t="b">
-        <v>0</v>
-      </c>
-      <c r="P16" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>0.03071177337325892</v>
-      </c>
-      <c r="R16" t="n">
-        <v>0</v>
-      </c>
-      <c r="S16" t="n">
-        <v>0.1016666666666683</v>
-      </c>
-      <c r="T16" t="b">
-        <v>0</v>
-      </c>
-      <c r="U16" t="n">
-        <v>8.359612132624427</v>
-      </c>
-      <c r="V16" t="n">
-        <v>6</v>
-      </c>
-      <c r="W16" t="n">
-        <v>0.1535512372287098</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>16</v>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>espontaneos</t>
-        </is>
-      </c>
-      <c r="C17" t="n">
-        <v>0</v>
-      </c>
-      <c r="D17" t="n">
-        <v>272</v>
-      </c>
-      <c r="E17" t="n">
-        <v>9.338333333333335</v>
-      </c>
-      <c r="F17" t="n">
-        <v>2.008200000000045</v>
-      </c>
-      <c r="G17" t="n">
-        <v>294.1947370693252</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0.6826090840390611</v>
-      </c>
-      <c r="I17" t="n">
-        <v>1</v>
-      </c>
-      <c r="J17" t="n">
-        <v>9.283307124765994</v>
-      </c>
-      <c r="K17" t="n">
-        <v>2</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0.05502620856734097</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0.1000000000000014</v>
-      </c>
-      <c r="O17" t="b">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>0.06638977509945043</v>
-      </c>
-      <c r="R17" t="n">
-        <v>0</v>
-      </c>
-      <c r="S17" t="n">
-        <v>0.1033333333333335</v>
-      </c>
-      <c r="T17" t="b">
-        <v>0</v>
-      </c>
-      <c r="U17" t="n">
-        <v>9.454144519370622</v>
-      </c>
-      <c r="V17" t="n">
-        <v>6</v>
-      </c>
-      <c r="W17" t="n">
-        <v>0.1708373946046287</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>17</v>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>espontaneos</t>
-        </is>
-      </c>
-      <c r="C18" t="n">
-        <v>0</v>
-      </c>
-      <c r="D18" t="n">
-        <v>290</v>
-      </c>
-      <c r="E18" t="n">
-        <v>9.938333333333334</v>
-      </c>
-      <c r="F18" t="n">
-        <v>2.204099999999983</v>
-      </c>
-      <c r="G18" t="n">
-        <v>294.2034913291759</v>
-      </c>
-      <c r="H18" t="n">
-        <v>0.7491753378051785</v>
-      </c>
-      <c r="I18" t="n">
-        <v>1</v>
-      </c>
-      <c r="J18" t="n">
-        <v>9.884551580034749</v>
-      </c>
-      <c r="K18" t="n">
-        <v>2</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0.05378175329858514</v>
-      </c>
-      <c r="M18" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" t="n">
-        <v>0.09999999999999964</v>
-      </c>
-      <c r="O18" t="b">
-        <v>0</v>
-      </c>
-      <c r="P18" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>0.0773669686169729</v>
-      </c>
-      <c r="R18" t="n">
-        <v>0.0400000000000027</v>
-      </c>
-      <c r="S18" t="n">
-        <v>0.1316666666666695</v>
-      </c>
-      <c r="T18" t="b">
-        <v>0</v>
-      </c>
-      <c r="U18" t="n">
-        <v>10.07473637722517</v>
-      </c>
-      <c r="V18" t="n">
-        <v>7</v>
-      </c>
-      <c r="W18" t="n">
-        <v>0.1901847971904207</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>18</v>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>espontaneos</t>
-        </is>
-      </c>
-      <c r="C19" t="n">
-        <v>0</v>
-      </c>
-      <c r="D19" t="n">
-        <v>308</v>
-      </c>
-      <c r="E19" t="n">
-        <v>10.53833333333333</v>
-      </c>
-      <c r="F19" t="n">
-        <v>2.337699999999984</v>
-      </c>
-      <c r="G19" t="n">
-        <v>294.214226572169</v>
-      </c>
-      <c r="H19" t="n">
-        <v>0.7945570910135985</v>
-      </c>
-      <c r="I19" t="n">
-        <v>1</v>
-      </c>
-      <c r="J19" t="n">
-        <v>10.46726430976431</v>
-      </c>
-      <c r="K19" t="n">
-        <v>3</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0.07106902356901834</v>
-      </c>
-      <c r="M19" t="n">
-        <v>0.04000000000000092</v>
-      </c>
-      <c r="N19" t="n">
-        <v>0.13333333333334</v>
-      </c>
-      <c r="O19" t="b">
-        <v>0</v>
-      </c>
-      <c r="P19" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>0.04524162297698275</v>
-      </c>
-      <c r="R19" t="n">
-        <v>0</v>
-      </c>
-      <c r="S19" t="n">
-        <v>0.09333333333333016</v>
-      </c>
-      <c r="T19" t="b">
-        <v>0</v>
-      </c>
-      <c r="U19" t="n">
-        <v>10.63149036402569</v>
-      </c>
-      <c r="V19" t="n">
-        <v>6</v>
-      </c>
-      <c r="W19" t="n">
-        <v>0.1642260542613805</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>19</v>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>espontaneos</t>
-        </is>
-      </c>
-      <c r="C20" t="n">
-        <v>0</v>
-      </c>
-      <c r="D20" t="n">
-        <v>342</v>
-      </c>
-      <c r="E20" t="n">
-        <v>11.67166666666667</v>
-      </c>
-      <c r="F20" t="n">
-        <v>2.003600000000006</v>
-      </c>
-      <c r="G20" t="n">
-        <v>294.2496961314322</v>
-      </c>
-      <c r="H20" t="n">
-        <v>0.6809182902622473</v>
-      </c>
-      <c r="I20" t="n">
-        <v>1</v>
-      </c>
-      <c r="J20" t="n">
-        <v>11.60524413625615</v>
-      </c>
-      <c r="K20" t="n">
-        <v>2</v>
-      </c>
-      <c r="L20" t="n">
-        <v>0.06642253041052015</v>
-      </c>
-      <c r="M20" t="n">
-        <v>0</v>
-      </c>
-      <c r="N20" t="n">
-        <v>0.09999999999999964</v>
-      </c>
-      <c r="O20" t="b">
-        <v>0</v>
-      </c>
-      <c r="P20" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>0.04391438782475277</v>
-      </c>
-      <c r="R20" t="n">
-        <v>0</v>
-      </c>
-      <c r="S20" t="n">
-        <v>0.09999999999999964</v>
-      </c>
-      <c r="T20" t="b">
-        <v>0</v>
-      </c>
-      <c r="U20" t="n">
-        <v>11.77693206064009</v>
-      </c>
-      <c r="V20" t="n">
-        <v>6</v>
-      </c>
-      <c r="W20" t="n">
-        <v>0.1716879243839351</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>20</v>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>estimulados</t>
-        </is>
-      </c>
-      <c r="C21" t="n">
-        <v>1</v>
-      </c>
-      <c r="D21" t="n">
-        <v>440</v>
-      </c>
-      <c r="E21" t="n">
-        <v>14.93833333333333</v>
-      </c>
-      <c r="F21" t="n">
-        <v>6.993899999999996</v>
-      </c>
-      <c r="G21" t="n">
-        <v>294.2013271098332</v>
-      </c>
-      <c r="H21" t="n">
-        <v>2.377249643537124</v>
-      </c>
-      <c r="I21" t="n">
-        <v>1</v>
-      </c>
-      <c r="J21" t="n">
-        <v>14.87483939589281</v>
-      </c>
-      <c r="K21" t="n">
-        <v>2</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0.06349393744052101</v>
-      </c>
-      <c r="M21" t="n">
-        <v>0</v>
-      </c>
-      <c r="N21" t="n">
-        <v>0.09999999999999964</v>
-      </c>
-      <c r="O21" t="b">
-        <v>0</v>
-      </c>
-      <c r="P21" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>0.06385769271328279</v>
-      </c>
-      <c r="R21" t="n">
-        <v>0</v>
-      </c>
-      <c r="S21" t="n">
-        <v>0.1066666666666709</v>
-      </c>
-      <c r="T21" t="b">
-        <v>0</v>
-      </c>
-      <c r="U21" t="n">
-        <v>15.06080248463021</v>
-      </c>
-      <c r="V21" t="n">
-        <v>6</v>
-      </c>
-      <c r="W21" t="n">
-        <v>0.1859630887374042</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>21</v>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>espontaneos</t>
-        </is>
-      </c>
-      <c r="C22" t="n">
-        <v>0</v>
-      </c>
-      <c r="D22" t="n">
-        <v>450</v>
-      </c>
-      <c r="E22" t="n">
-        <v>15.27833333333333</v>
-      </c>
-      <c r="F22" t="n">
-        <v>1.662700000000029</v>
-      </c>
-      <c r="G22" t="n">
-        <v>294.156462528554</v>
-      </c>
-      <c r="H22" t="n">
-        <v>0.5652434033600842</v>
-      </c>
-      <c r="I22" t="n">
-        <v>1</v>
-      </c>
-      <c r="J22" t="n">
-        <v>15.21000861528822</v>
-      </c>
-      <c r="K22" t="n">
-        <v>2</v>
-      </c>
-      <c r="L22" t="n">
-        <v>0.06832471804511009</v>
-      </c>
-      <c r="M22" t="n">
-        <v>0</v>
-      </c>
-      <c r="N22" t="n">
-        <v>0.09833333333332916</v>
-      </c>
-      <c r="O22" t="b">
-        <v>0</v>
-      </c>
-      <c r="P22" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>0.03594812742143461</v>
-      </c>
-      <c r="R22" t="n">
-        <v>0</v>
-      </c>
-      <c r="S22" t="n">
-        <v>0.1016666666666595</v>
-      </c>
-      <c r="T22" t="b">
-        <v>0</v>
-      </c>
-      <c r="U22" t="n">
-        <v>15.35982679647658</v>
-      </c>
-      <c r="V22" t="n">
-        <v>5</v>
-      </c>
-      <c r="W22" t="n">
-        <v>0.1498181811883619</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>22</v>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>espontaneos</t>
-        </is>
-      </c>
-      <c r="C23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D23" t="n">
-        <v>458</v>
-      </c>
-      <c r="E23" t="n">
-        <v>15.55</v>
-      </c>
-      <c r="F23" t="n">
-        <v>1.886000000000024</v>
-      </c>
-      <c r="G23" t="n">
-        <v>294.1186033098033</v>
-      </c>
-      <c r="H23" t="n">
-        <v>0.6412379151731004</v>
-      </c>
-      <c r="I23" t="n">
-        <v>1</v>
-      </c>
-      <c r="J23" t="n">
-        <v>15.47975843239103</v>
-      </c>
-      <c r="K23" t="n">
-        <v>2</v>
-      </c>
-      <c r="L23" t="n">
-        <v>0.07024156760896716</v>
-      </c>
-      <c r="M23" t="n">
-        <v>0</v>
-      </c>
-      <c r="N23" t="n">
-        <v>0.09999999999999964</v>
-      </c>
-      <c r="O23" t="b">
-        <v>0</v>
-      </c>
-      <c r="P23" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>0.03859905521109752</v>
-      </c>
-      <c r="R23" t="n">
-        <v>0</v>
-      </c>
-      <c r="S23" t="n">
-        <v>0.09333333333333016</v>
-      </c>
-      <c r="T23" t="b">
-        <v>0</v>
-      </c>
-      <c r="U23" t="n">
-        <v>15.62125419354839</v>
-      </c>
-      <c r="V23" t="n">
-        <v>5</v>
-      </c>
-      <c r="W23" t="n">
-        <v>0.1414957611573548</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>23</v>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>espontaneos</t>
-        </is>
-      </c>
-      <c r="C24" t="n">
-        <v>0</v>
-      </c>
-      <c r="D24" t="n">
-        <v>467</v>
-      </c>
-      <c r="E24" t="n">
-        <v>15.83833333333333</v>
-      </c>
-      <c r="F24" t="n">
-        <v>1.691100000000006</v>
-      </c>
-      <c r="G24" t="n">
-        <v>294.1159046764793</v>
-      </c>
-      <c r="H24" t="n">
-        <v>0.5749774062236371</v>
-      </c>
-      <c r="I24" t="n">
-        <v>2</v>
-      </c>
-      <c r="J24" t="n">
-        <v>15.76352863317127</v>
-      </c>
-      <c r="K24" t="n">
-        <v>3</v>
-      </c>
-      <c r="L24" t="n">
-        <v>0.07480470016206375</v>
-      </c>
-      <c r="M24" t="n">
-        <v>0</v>
-      </c>
-      <c r="N24" t="n">
-        <v>0.1333333333333293</v>
-      </c>
-      <c r="O24" t="b">
-        <v>0</v>
-      </c>
-      <c r="P24" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>0.04981108035675774</v>
-      </c>
-      <c r="R24" t="n">
-        <v>0</v>
-      </c>
-      <c r="S24" t="n">
-        <v>0.1316666666666588</v>
-      </c>
-      <c r="T24" t="b">
-        <v>0</v>
-      </c>
-      <c r="U24" t="n">
-        <v>15.94463069544365</v>
-      </c>
-      <c r="V24" t="n">
-        <v>7</v>
-      </c>
-      <c r="W24" t="n">
-        <v>0.1811020622723802</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="n">
-        <v>24</v>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>espontaneos</t>
-        </is>
-      </c>
-      <c r="C25" t="n">
-        <v>0</v>
-      </c>
-      <c r="D25" t="n">
-        <v>481</v>
-      </c>
-      <c r="E25" t="n">
-        <v>16.305</v>
-      </c>
-      <c r="F25" t="n">
-        <v>1.300000000000011</v>
-      </c>
-      <c r="G25" t="n">
-        <v>294.1511484325548</v>
-      </c>
-      <c r="H25" t="n">
-        <v>0.4419496598695365</v>
-      </c>
-      <c r="I25" t="n">
-        <v>2</v>
-      </c>
-      <c r="J25" t="n">
-        <v>16.24686112692089</v>
-      </c>
-      <c r="K25" t="n">
-        <v>2</v>
-      </c>
-      <c r="L25" t="n">
-        <v>0.05813887307911259</v>
-      </c>
-      <c r="M25" t="n">
-        <v>0</v>
-      </c>
-      <c r="N25" t="n">
-        <v>0.13333333333334</v>
-      </c>
-      <c r="O25" t="b">
-        <v>0</v>
-      </c>
-      <c r="P25" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>0.07519988155167567</v>
-      </c>
-      <c r="R25" t="n">
-        <v>0</v>
-      </c>
-      <c r="S25" t="n">
-        <v>0.1316666666666713</v>
-      </c>
-      <c r="T25" t="b">
-        <v>0</v>
-      </c>
-      <c r="U25" t="n">
-        <v>16.45064314590225</v>
-      </c>
-      <c r="V25" t="n">
-        <v>7</v>
-      </c>
-      <c r="W25" t="n">
-        <v>0.2037820189813608</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="n">
-        <v>25</v>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>estimulados</t>
-        </is>
-      </c>
-      <c r="C26" t="n">
-        <v>1</v>
-      </c>
-      <c r="D26" t="n">
-        <v>740</v>
-      </c>
-      <c r="E26" t="n">
-        <v>24.93666666666667</v>
-      </c>
-      <c r="F26" t="n">
-        <v>7.032300000000021</v>
-      </c>
-      <c r="G26" t="n">
-        <v>294.2397232959302</v>
-      </c>
-      <c r="H26" t="n">
-        <v>2.389990012642623</v>
-      </c>
-      <c r="I26" t="n">
-        <v>1</v>
-      </c>
-      <c r="J26" t="n">
-        <v>24.87587979664488</v>
-      </c>
-      <c r="K26" t="n">
-        <v>2</v>
-      </c>
-      <c r="L26" t="n">
-        <v>0.06078687002178995</v>
-      </c>
-      <c r="M26" t="n">
-        <v>0</v>
-      </c>
-      <c r="N26" t="n">
-        <v>0.1016666666666701</v>
-      </c>
-      <c r="O26" t="b">
-        <v>0</v>
-      </c>
-      <c r="P26" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>0.05946369636963311</v>
-      </c>
-      <c r="R26" t="n">
-        <v>0</v>
-      </c>
-      <c r="S26" t="n">
-        <v>0.09833333333332916</v>
-      </c>
-      <c r="T26" t="b">
-        <v>0</v>
-      </c>
-      <c r="U26" t="n">
-        <v>25.06408252781716</v>
-      </c>
-      <c r="V26" t="n">
-        <v>6</v>
-      </c>
-      <c r="W26" t="n">
-        <v>0.1882027311722823</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="n">
-        <v>26</v>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>estimulados</t>
-        </is>
-      </c>
-      <c r="C27" t="n">
-        <v>1</v>
-      </c>
-      <c r="D27" t="n">
-        <v>1040</v>
-      </c>
-      <c r="E27" t="n">
-        <v>34.93666666666667</v>
-      </c>
-      <c r="F27" t="n">
-        <v>6.870100000000036</v>
-      </c>
-      <c r="G27" t="n">
-        <v>294.1919757127387</v>
-      </c>
-      <c r="H27" t="n">
-        <v>2.335243843193156</v>
-      </c>
-      <c r="I27" t="n">
-        <v>1</v>
-      </c>
-      <c r="J27" t="n">
-        <v>34.87568189346437</v>
-      </c>
-      <c r="K27" t="n">
-        <v>2</v>
-      </c>
-      <c r="L27" t="n">
-        <v>0.06098477320229989</v>
-      </c>
-      <c r="M27" t="n">
-        <v>0</v>
-      </c>
-      <c r="N27" t="n">
-        <v>0.09833333333332916</v>
-      </c>
-      <c r="O27" t="b">
-        <v>0</v>
-      </c>
-      <c r="P27" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>0.06340293333334301</v>
-      </c>
-      <c r="R27" t="n">
-        <v>0</v>
-      </c>
-      <c r="S27" t="n">
-        <v>0.1033333333333388</v>
-      </c>
-      <c r="T27" t="b">
-        <v>0</v>
-      </c>
-      <c r="U27" t="n">
-        <v>35.0598166372722</v>
-      </c>
-      <c r="V27" t="n">
-        <v>6</v>
-      </c>
-      <c r="W27" t="n">
-        <v>0.1841347438078316</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="n">
-        <v>27</v>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>estimulados</t>
-        </is>
-      </c>
-      <c r="C28" t="n">
-        <v>1</v>
-      </c>
-      <c r="D28" t="n">
-        <v>1340</v>
-      </c>
-      <c r="E28" t="n">
-        <v>44.94333333333334</v>
-      </c>
-      <c r="F28" t="n">
-        <v>6.675000000000011</v>
-      </c>
-      <c r="G28" t="n">
-        <v>294.1677991825379</v>
-      </c>
-      <c r="H28" t="n">
-        <v>2.269113077144796</v>
-      </c>
-      <c r="I28" t="n">
-        <v>1</v>
-      </c>
-      <c r="J28" t="n">
-        <v>44.87580165150298</v>
-      </c>
-      <c r="K28" t="n">
-        <v>2</v>
-      </c>
-      <c r="L28" t="n">
-        <v>0.06753168183035996</v>
-      </c>
-      <c r="M28" t="n">
-        <v>0</v>
-      </c>
-      <c r="N28" t="n">
-        <v>0.1049999999999969</v>
-      </c>
-      <c r="O28" t="b">
-        <v>0</v>
-      </c>
-      <c r="P28" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>0.05389935763220421</v>
-      </c>
-      <c r="R28" t="n">
-        <v>0</v>
-      </c>
-      <c r="S28" t="n">
-        <v>0.09833333333333627</v>
-      </c>
-      <c r="T28" t="b">
-        <v>0</v>
-      </c>
-      <c r="U28" t="n">
-        <v>45.06119392119393</v>
-      </c>
-      <c r="V28" t="n">
-        <v>6</v>
-      </c>
-      <c r="W28" t="n">
-        <v>0.1853922696909436</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="n">
-        <v>28</v>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>estimulados</t>
-        </is>
-      </c>
-      <c r="C29" t="n">
-        <v>1</v>
-      </c>
-      <c r="D29" t="n">
-        <v>1640</v>
-      </c>
-      <c r="E29" t="n">
-        <v>54.93666666666667</v>
-      </c>
-      <c r="F29" t="n">
-        <v>6.613</v>
-      </c>
-      <c r="G29" t="n">
-        <v>294.1908725605803</v>
-      </c>
-      <c r="H29" t="n">
-        <v>2.247860357611278</v>
-      </c>
-      <c r="I29" t="n">
-        <v>1</v>
-      </c>
-      <c r="J29" t="n">
-        <v>54.87984217671682</v>
-      </c>
-      <c r="K29" t="n">
-        <v>2</v>
-      </c>
-      <c r="L29" t="n">
-        <v>0.05682448994984668</v>
-      </c>
-      <c r="M29" t="n">
-        <v>0</v>
-      </c>
-      <c r="N29" t="n">
-        <v>0.1016666666666666</v>
-      </c>
-      <c r="O29" t="b">
-        <v>0</v>
-      </c>
-      <c r="P29" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>0.06207670532109688</v>
-      </c>
-      <c r="R29" t="n">
-        <v>0</v>
-      </c>
-      <c r="S29" t="n">
-        <v>0.1000000000000014</v>
-      </c>
-      <c r="T29" t="b">
-        <v>0</v>
-      </c>
-      <c r="U29" t="n">
-        <v>55.06085729759004</v>
-      </c>
-      <c r="V29" t="n">
-        <v>6</v>
-      </c>
-      <c r="W29" t="n">
-        <v>0.1810151208732194</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="n">
-        <v>29</v>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>estimulados</t>
-        </is>
-      </c>
-      <c r="C30" t="n">
-        <v>1</v>
-      </c>
-      <c r="D30" t="n">
-        <v>1940</v>
-      </c>
-      <c r="E30" t="n">
-        <v>64.94</v>
-      </c>
-      <c r="F30" t="n">
-        <v>6.744799999999998</v>
-      </c>
-      <c r="G30" t="n">
-        <v>294.1102572478562</v>
-      </c>
-      <c r="H30" t="n">
-        <v>2.293289619721062</v>
-      </c>
-      <c r="I30" t="n">
-        <v>1</v>
-      </c>
-      <c r="J30" t="n">
-        <v>64.87544567409766</v>
-      </c>
-      <c r="K30" t="n">
-        <v>2</v>
-      </c>
-      <c r="L30" t="n">
-        <v>0.06455432590233556</v>
-      </c>
-      <c r="M30" t="n">
-        <v>0</v>
-      </c>
-      <c r="N30" t="n">
-        <v>0.09833333333332916</v>
-      </c>
-      <c r="O30" t="b">
-        <v>0</v>
-      </c>
-      <c r="P30" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>0.05568519369163027</v>
-      </c>
-      <c r="R30" t="n">
-        <v>0</v>
-      </c>
-      <c r="S30" t="n">
-        <v>0.1016666666666595</v>
-      </c>
-      <c r="T30" t="b">
-        <v>0</v>
-      </c>
-      <c r="U30" t="n">
-        <v>65.05270866845399</v>
-      </c>
-      <c r="V30" t="n">
-        <v>6</v>
-      </c>
-      <c r="W30" t="n">
-        <v>0.177262994356326</v>
+          <t>17 contraccion(es) en 10.0 s; amplitud mediana 0.71 %; frecuencia mediana 1.76 Hz (IQR 1.67-1.77); actividad basal 0.67 % del grosor</t>
+        </is>
       </c>
     </row>
   </sheetData>
